--- a/ECON251/Tutorial/T01/Assignment 1 template (To submit on Moodle) .xlsx
+++ b/ECON251/Tutorial/T01/Assignment 1 template (To submit on Moodle) .xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wizlinkconsultingpteltd-my.sharepoint.com/personal/clare_kon_wizlink_biz/Documents/UOW2026/tutorial/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{541FDE5E-DE0A-48FD-A2A3-0B2ADFB086E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{433F9DEF-3CDA-471D-9EA6-9DB6DD98F9CD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4194DFE3-4B0E-4C89-B4C2-AFBAB98626AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13276" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="sg" sheetId="10" r:id="rId2"/>
-    <sheet name="Country Assigned" sheetId="16" r:id="rId3"/>
+    <sheet name="Country Assigned" sheetId="16" r:id="rId2"/>
+    <sheet name="sg" sheetId="10" r:id="rId3"/>
     <sheet name="regression 1 _SG" sheetId="11" r:id="rId4"/>
     <sheet name="regression 2_SG" sheetId="12" r:id="rId5"/>
     <sheet name="regression 3_sg" sheetId="17" r:id="rId6"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="176">
   <si>
     <t>Development relevance</t>
   </si>
@@ -621,15 +621,42 @@
   <si>
     <t>h</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">at least completed  upper seondary </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> post-secondary, population 25+, total (%) </t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -671,6 +698,14 @@
     </font>
     <font>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -781,7 +816,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -891,9 +926,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -939,16 +971,23 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="5" fillId="10" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="6" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="10" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4221,7 +4260,7 @@
             <c:numRef>
               <c:f>'[1]chart 1_sg'!$B$2:$B$26</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>25.861486037755899</c:v>
@@ -4435,7 +4474,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -8733,63 +8772,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="16" max="16" width="17.86328125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" ht="151.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" s="2" customFormat="1" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="J1" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="64" t="s">
         <v>140</v>
+      </c>
+      <c r="R1" s="64" t="s">
+        <v>161</v>
+      </c>
+      <c r="S1" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="T1" s="64" t="s">
+        <v>163</v>
+      </c>
+      <c r="U1" s="64" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -8798,1838 +8846,33 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1524E039-9D98-4AD9-9E87-88901946F8BA}">
-  <dimension ref="A1:AG29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8A5EBE0-77D1-4DEE-BD25-B861D3CF253E}">
+  <dimension ref="A1:AJ29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.06640625" style="3"/>
-    <col min="3" max="3" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.06640625" style="53"/>
-    <col min="9" max="9" width="17.53125" style="6" customWidth="1"/>
-    <col min="10" max="10" width="18.9296875" style="6" customWidth="1"/>
-    <col min="11" max="11" width="9.06640625" style="43"/>
-    <col min="12" max="12" width="12.19921875" style="6" customWidth="1"/>
-    <col min="13" max="13" width="12.19921875" style="9" customWidth="1"/>
-    <col min="14" max="14" width="9.06640625" style="6"/>
-    <col min="15" max="15" width="9.06640625" style="43"/>
-    <col min="16" max="16" width="9.06640625" style="50"/>
-    <col min="17" max="17" width="15.59765625" customWidth="1"/>
-    <col min="18" max="18" width="13.33203125" style="25" customWidth="1"/>
-    <col min="25" max="25" width="14.86328125" style="25" customWidth="1"/>
-    <col min="28" max="28" width="11.59765625" style="25" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.53125" customWidth="1"/>
-    <col min="30" max="33" width="9.06640625" style="2"/>
+    <col min="3" max="3" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="3"/>
+    <col min="5" max="5" width="3.28515625" style="28" customWidth="1"/>
+    <col min="6" max="6" width="9" style="3"/>
+    <col min="8" max="8" width="5" style="29" customWidth="1"/>
+    <col min="11" max="11" width="17.5703125" style="6" customWidth="1"/>
+    <col min="12" max="13" width="9" style="6"/>
+    <col min="14" max="14" width="12.140625" style="6" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" style="9" customWidth="1"/>
+    <col min="16" max="16" width="9" style="6"/>
+    <col min="17" max="17" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.140625" style="31" customWidth="1"/>
+    <col min="19" max="19" width="13.28515625" customWidth="1"/>
+    <col min="20" max="20" width="13.28515625" style="25" customWidth="1"/>
+    <col min="21" max="21" width="4.42578125" style="29" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" customWidth="1"/>
+    <col min="29" max="29" width="3.7109375" style="29" customWidth="1"/>
+    <col min="31" max="31" width="9" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="2" customFormat="1" ht="151.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="K1" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="O1" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="R1" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y1" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB1" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" s="57" customFormat="1" ht="108.4" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C2" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="E2" s="57" t="s">
-        <v>171</v>
-      </c>
-      <c r="I2" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="J2" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="K2" s="59"/>
-      <c r="L2" s="56" t="s">
-        <v>172</v>
-      </c>
-      <c r="M2" s="60"/>
-      <c r="N2" s="58" t="s">
-        <v>173</v>
-      </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="57" t="s">
-        <v>174</v>
-      </c>
-      <c r="R2" s="54" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y2" s="54" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB2" s="54" t="s">
-        <v>152</v>
-      </c>
-      <c r="AD2" s="55" t="s">
-        <v>165</v>
-      </c>
-      <c r="AE2" s="55" t="s">
-        <v>166</v>
-      </c>
-      <c r="AF2" s="55" t="s">
-        <v>167</v>
-      </c>
-      <c r="AG2" s="55" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="3">
-        <v>2000</v>
-      </c>
-      <c r="C3">
-        <v>140533304238.72125</v>
-      </c>
-      <c r="D3">
-        <v>9.0383163255516337</v>
-      </c>
-      <c r="E3">
-        <v>43703162220.646263</v>
-      </c>
-      <c r="F3">
-        <v>11.414764762166143</v>
-      </c>
-      <c r="G3">
-        <v>2138100</v>
-      </c>
-      <c r="H3" s="53">
-        <v>3.7</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>169</v>
-      </c>
-      <c r="S3">
-        <v>25.861486037755899</v>
-      </c>
-      <c r="T3">
-        <v>15.146298038161788</v>
-      </c>
-      <c r="U3">
-        <v>29918062298.838032</v>
-      </c>
-      <c r="V3">
-        <v>9.2131732680321002E-2</v>
-      </c>
-      <c r="W3">
-        <v>0.17689908365402099</v>
-      </c>
-      <c r="X3">
-        <v>27.293652478865699</v>
-      </c>
-      <c r="Z3">
-        <v>72.529399958696104</v>
-      </c>
-      <c r="AA3">
-        <v>3.26034372238966E-4</v>
-      </c>
-      <c r="AD3">
-        <v>10.504164644115525</v>
-      </c>
-      <c r="AE3">
-        <v>41.855216732958041</v>
-      </c>
-      <c r="AF3">
-        <v>32.326344362576407</v>
-      </c>
-      <c r="AG3">
-        <v>12.337260101284532</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2001</v>
-      </c>
-      <c r="C4">
-        <v>139028385430.87299</v>
-      </c>
-      <c r="D4">
-        <v>-1.0708627510044835</v>
-      </c>
-      <c r="E4">
-        <v>41427454403.287689</v>
-      </c>
-      <c r="F4">
-        <v>-5.2071925730891024</v>
-      </c>
-      <c r="G4">
-        <v>2205923</v>
-      </c>
-      <c r="H4" s="53">
-        <v>3.76</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>169</v>
-      </c>
-      <c r="S4">
-        <v>23.394697847414562</v>
-      </c>
-      <c r="T4">
-        <v>-11.605048125430017</v>
-      </c>
-      <c r="U4">
-        <v>26446056770.861744</v>
-      </c>
-      <c r="V4">
-        <v>8.2356655909540694E-2</v>
-      </c>
-      <c r="W4">
-        <v>0.173741005150197</v>
-      </c>
-      <c r="X4">
-        <v>26.157941891234099</v>
-      </c>
-      <c r="Z4">
-        <v>73.668317103615706</v>
-      </c>
-      <c r="AA4">
-        <v>4.0237915923044699E-4</v>
-      </c>
-      <c r="AD4">
-        <v>11.609926556509718</v>
-      </c>
-      <c r="AE4">
-        <v>46.244971582292017</v>
-      </c>
-      <c r="AF4">
-        <v>30.887040232314138</v>
-      </c>
-      <c r="AG4">
-        <v>16.496255724564534</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="3">
-        <v>2002</v>
-      </c>
-      <c r="C5">
-        <v>144482970559.8894</v>
-      </c>
-      <c r="D5">
-        <v>3.923360767020128</v>
-      </c>
-      <c r="E5">
-        <v>37635189933.264236</v>
-      </c>
-      <c r="F5">
-        <v>-9.1539886402542265</v>
-      </c>
-      <c r="G5">
-        <v>2200772</v>
-      </c>
-      <c r="H5" s="53">
-        <v>5.65</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>169</v>
-      </c>
-      <c r="S5">
-        <v>24.737640322972926</v>
-      </c>
-      <c r="T5">
-        <v>8.4686746225800107</v>
-      </c>
-      <c r="U5">
-        <v>28685687269.288815</v>
-      </c>
-      <c r="V5">
-        <v>7.1032800014001363E-2</v>
-      </c>
-      <c r="W5">
-        <v>0.16944763175838501</v>
-      </c>
-      <c r="X5">
-        <v>25.389889592307298</v>
-      </c>
-      <c r="Z5">
-        <v>74.440662775934399</v>
-      </c>
-      <c r="AA5">
-        <v>4.3398819080536202E-4</v>
-      </c>
-      <c r="AD5">
-        <v>11.84032888729563</v>
-      </c>
-      <c r="AE5">
-        <v>46.182484892705467</v>
-      </c>
-      <c r="AF5">
-        <v>26.751423220905973</v>
-      </c>
-      <c r="AG5">
-        <v>18.426222147387328</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="3">
-        <v>2003</v>
-      </c>
-      <c r="C6">
-        <v>151054425108.65015</v>
-      </c>
-      <c r="D6">
-        <v>4.5482554264322914</v>
-      </c>
-      <c r="E6">
-        <v>35694579310.094017</v>
-      </c>
-      <c r="F6">
-        <v>-5.1563726039681654</v>
-      </c>
-      <c r="G6">
-        <v>2176377</v>
-      </c>
-      <c r="H6" s="53">
-        <v>5.93</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>169</v>
-      </c>
-      <c r="S6">
-        <v>24.765412693196893</v>
-      </c>
-      <c r="T6">
-        <v>2.9963638945377227</v>
-      </c>
-      <c r="U6">
-        <v>29545214845.525787</v>
-      </c>
-      <c r="V6">
-        <v>6.1134072311026647E-2</v>
-      </c>
-      <c r="W6">
-        <v>0.16459654177274699</v>
-      </c>
-      <c r="X6">
-        <v>24.785305691086901</v>
-      </c>
-      <c r="Z6">
-        <v>75.050049199261395</v>
-      </c>
-      <c r="AA6">
-        <v>5.9371726127004001E-4</v>
-      </c>
-      <c r="AD6">
-        <v>11.4140839970397</v>
-      </c>
-      <c r="AE6">
-        <v>45.535361064297177</v>
-      </c>
-      <c r="AF6">
-        <v>24.766294434624459</v>
-      </c>
-      <c r="AG6">
-        <v>27.953848478026121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="3">
-        <v>2004</v>
-      </c>
-      <c r="C7">
-        <v>166069208808.39377</v>
-      </c>
-      <c r="D7">
-        <v>9.9399826843495731</v>
-      </c>
-      <c r="E7">
-        <v>39369010601.349266</v>
-      </c>
-      <c r="F7">
-        <v>10.294087680187801</v>
-      </c>
-      <c r="G7">
-        <v>2211220</v>
-      </c>
-      <c r="H7" s="53">
-        <v>5.84</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>169</v>
-      </c>
-      <c r="S7">
-        <v>27.119367597064286</v>
-      </c>
-      <c r="T7">
-        <v>13.8458129716023</v>
-      </c>
-      <c r="U7">
-        <v>33635990035.095367</v>
-      </c>
-      <c r="V7">
-        <v>5.5648989626246571E-2</v>
-      </c>
-      <c r="W7">
-        <v>0.15970081754349399</v>
-      </c>
-      <c r="X7">
-        <v>24.4105337316422</v>
-      </c>
-      <c r="Z7">
-        <v>75.429717492610806</v>
-      </c>
-      <c r="AA7">
-        <v>5.5564498338846495E-4</v>
-      </c>
-      <c r="AD7">
-        <v>10.318670184588006</v>
-      </c>
-      <c r="AE7">
-        <v>41.998426193084512</v>
-      </c>
-      <c r="AF7">
-        <v>24.281423420921346</v>
-      </c>
-      <c r="AG7">
-        <v>26.379678346782697</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="3">
-        <v>2005</v>
-      </c>
-      <c r="C8">
-        <v>178302402123.90665</v>
-      </c>
-      <c r="D8">
-        <v>7.366322392507584</v>
-      </c>
-      <c r="E8">
-        <v>40801992980.92485</v>
-      </c>
-      <c r="F8">
-        <v>3.6398739965450631</v>
-      </c>
-      <c r="G8">
-        <v>2301785</v>
-      </c>
-      <c r="H8" s="53">
-        <v>5.59</v>
-      </c>
-      <c r="Q8">
-        <v>38.256099700927699</v>
-      </c>
-      <c r="S8">
-        <v>27.076761798207059</v>
-      </c>
-      <c r="T8">
-        <v>9.5096402529214856</v>
-      </c>
-      <c r="U8">
-        <v>36834651682.94146</v>
-      </c>
-      <c r="V8">
-        <v>5.5048114214259862E-2</v>
-      </c>
-      <c r="W8">
-        <v>0.155212233759282</v>
-      </c>
-      <c r="X8">
-        <v>23.882954799438199</v>
-      </c>
-      <c r="Z8">
-        <v>75.961878955612505</v>
-      </c>
-      <c r="AA8">
-        <v>5.4706140442952399E-4</v>
-      </c>
-      <c r="AD8">
-        <v>9.8971432332187881</v>
-      </c>
-      <c r="AE8">
-        <v>39.847877286424129</v>
-      </c>
-      <c r="AF8">
-        <v>23.187995656323011</v>
-      </c>
-      <c r="AG8">
-        <v>29.88882255327351</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="3">
-        <v>2006</v>
-      </c>
-      <c r="C9">
-        <v>194361682395.94128</v>
-      </c>
-      <c r="D9">
-        <v>9.0067660787175754</v>
-      </c>
-      <c r="E9">
-        <v>44652955830.742096</v>
-      </c>
-      <c r="F9">
-        <v>9.4381734039746306</v>
-      </c>
-      <c r="G9">
-        <v>2426201</v>
-      </c>
-      <c r="H9" s="53">
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="Q9">
-        <v>36.755790710449197</v>
-      </c>
-      <c r="S9">
-        <v>26.578005985802772</v>
-      </c>
-      <c r="T9">
-        <v>11.921913382779238</v>
-      </c>
-      <c r="U9">
-        <v>41226046951.430176</v>
-      </c>
-      <c r="V9">
-        <v>4.8865424451682515E-2</v>
-      </c>
-      <c r="W9">
-        <v>0.15069969562712299</v>
-      </c>
-      <c r="X9">
-        <v>23.2978195732057</v>
-      </c>
-      <c r="Z9">
-        <v>76.5515238251608</v>
-      </c>
-      <c r="AA9">
-        <v>3.65545459554034E-3</v>
-      </c>
-      <c r="AD9">
-        <v>9.9069355027210513</v>
-      </c>
-      <c r="AE9">
-        <v>38.106096406316425</v>
-      </c>
-      <c r="AF9">
-        <v>23.086711145212458</v>
-      </c>
-      <c r="AG9">
-        <v>30.711834579105247</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="3">
-        <v>2007</v>
-      </c>
-      <c r="C10">
-        <v>211896059498.4816</v>
-      </c>
-      <c r="D10">
-        <v>9.0215195126889256</v>
-      </c>
-      <c r="E10">
-        <v>51576309712.14518</v>
-      </c>
-      <c r="F10">
-        <v>15.504805342889711</v>
-      </c>
-      <c r="G10">
-        <v>2530038</v>
-      </c>
-      <c r="H10" s="53">
-        <v>3.9</v>
-      </c>
-      <c r="Q10">
-        <v>37.784400939941399</v>
-      </c>
-      <c r="S10">
-        <v>23.822651904527213</v>
-      </c>
-      <c r="T10">
-        <v>5.9408665704516324</v>
-      </c>
-      <c r="U10">
-        <v>43675231393.086388</v>
-      </c>
-      <c r="V10">
-        <v>4.286799737144735E-2</v>
-      </c>
-      <c r="W10">
-        <v>0.14645508484910399</v>
-      </c>
-      <c r="X10">
-        <v>23.590067003098699</v>
-      </c>
-      <c r="Z10">
-        <v>76.263477912052196</v>
-      </c>
-      <c r="AA10">
-        <v>6.8551812889980296E-3</v>
-      </c>
-      <c r="AD10">
-        <v>9.1361273439883615</v>
-      </c>
-      <c r="AE10">
-        <v>36.765963470158894</v>
-      </c>
-      <c r="AF10">
-        <v>24.375682074209674</v>
-      </c>
-      <c r="AG10">
-        <v>31.270315543664491</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="3">
-        <v>2008</v>
-      </c>
-      <c r="C11">
-        <v>215844707508.2283</v>
-      </c>
-      <c r="D11">
-        <v>1.8634834546203507</v>
-      </c>
-      <c r="E11">
-        <v>57123779390.104187</v>
-      </c>
-      <c r="F11">
-        <v>10.755848390317652</v>
-      </c>
-      <c r="G11">
-        <v>2737323</v>
-      </c>
-      <c r="H11" s="53">
-        <v>3.96</v>
-      </c>
-      <c r="Q11">
-        <v>40.407138824462898</v>
-      </c>
-      <c r="S11">
-        <v>20.585664973848445</v>
-      </c>
-      <c r="T11">
-        <v>-4.1884694683058541</v>
-      </c>
-      <c r="U11">
-        <v>41845907660.975029</v>
-      </c>
-      <c r="V11">
-        <v>4.1432188466446869E-2</v>
-      </c>
-      <c r="W11">
-        <v>0.14231124802675299</v>
-      </c>
-      <c r="X11">
-        <v>23.729672967526501</v>
-      </c>
-      <c r="Z11">
-        <v>76.128015784446703</v>
-      </c>
-      <c r="AA11">
-        <v>2.5386566425965599E-2</v>
-      </c>
-      <c r="AD11">
-        <v>10.113213911286202</v>
-      </c>
-      <c r="AE11">
-        <v>39.95092384654248</v>
-      </c>
-      <c r="AF11">
-        <v>27.978919594541324</v>
-      </c>
-      <c r="AG11">
-        <v>20.660826979180964</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="3">
-        <v>2009</v>
-      </c>
-      <c r="C12">
-        <v>216120888113.03256</v>
-      </c>
-      <c r="D12">
-        <v>0.1279533827780881</v>
-      </c>
-      <c r="E12">
-        <v>60258141945.338493</v>
-      </c>
-      <c r="F12">
-        <v>5.4869663539406588</v>
-      </c>
-      <c r="G12">
-        <v>2837096</v>
-      </c>
-      <c r="H12" s="53">
-        <v>5.86</v>
-      </c>
-      <c r="Q12">
-        <v>40.729148864746101</v>
-      </c>
-      <c r="S12">
-        <v>20.273376429073512</v>
-      </c>
-      <c r="T12">
-        <v>-4.1502986226508227</v>
-      </c>
-      <c r="U12">
-        <v>40109177531.685844</v>
-      </c>
-      <c r="V12">
-        <v>4.0687761270138054E-2</v>
-      </c>
-      <c r="W12">
-        <v>0.13906365808080101</v>
-      </c>
-      <c r="X12">
-        <v>22.593183926345901</v>
-      </c>
-      <c r="Z12">
-        <v>77.267790000345798</v>
-      </c>
-      <c r="AA12">
-        <v>6.7856716847083803E-3</v>
-      </c>
-      <c r="AD12">
-        <v>9.9299738486408202</v>
-      </c>
-      <c r="AE12">
-        <v>39.102921622057082</v>
-      </c>
-      <c r="AF12">
-        <v>28.837459653073982</v>
-      </c>
-      <c r="AG12">
-        <v>23.497058193413821</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="3">
-        <v>2010</v>
-      </c>
-      <c r="C13">
-        <v>247501100140.01782</v>
-      </c>
-      <c r="D13">
-        <v>14.519749710899404</v>
-      </c>
-      <c r="E13">
-        <v>64325859654.865166</v>
-      </c>
-      <c r="F13">
-        <v>6.7504864541236316</v>
-      </c>
-      <c r="G13">
-        <v>2936802</v>
-      </c>
-      <c r="H13" s="53">
-        <v>4.12</v>
-      </c>
-      <c r="Q13">
-        <v>46.475578308105497</v>
-      </c>
-      <c r="S13">
-        <v>20.773833025312548</v>
-      </c>
-      <c r="T13">
-        <v>29.675335626760187</v>
-      </c>
-      <c r="U13">
-        <v>52011710581.34671</v>
-      </c>
-      <c r="V13">
-        <v>3.614898888342135E-2</v>
-      </c>
-      <c r="W13">
-        <v>0.13561924621409599</v>
-      </c>
-      <c r="X13">
-        <v>21.723582478803099</v>
-      </c>
-      <c r="Z13">
-        <v>78.140762763266096</v>
-      </c>
-      <c r="AA13">
-        <v>3.8512160672045999E-2</v>
-      </c>
-      <c r="AD13">
-        <v>9.6915683859659953</v>
-      </c>
-      <c r="AE13">
-        <v>36.337838296581353</v>
-      </c>
-      <c r="AF13">
-        <v>25.569721215450116</v>
-      </c>
-      <c r="AG13">
-        <v>26.312365798407917</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="3">
-        <v>2011</v>
-      </c>
-      <c r="C14">
-        <v>262883130580.25568</v>
-      </c>
-      <c r="D14">
-        <v>6.2149341685898918</v>
-      </c>
-      <c r="E14">
-        <v>68420489880.530258</v>
-      </c>
-      <c r="F14">
-        <v>6.3654496770575264</v>
-      </c>
-      <c r="G14">
-        <v>3012462</v>
-      </c>
-      <c r="H14" s="53">
-        <v>3.89</v>
-      </c>
-      <c r="Q14">
-        <v>46.935169219970703</v>
-      </c>
-      <c r="S14">
-        <v>19.582551507977822</v>
-      </c>
-      <c r="T14">
-        <v>7.8077670717552081</v>
-      </c>
-      <c r="U14">
-        <v>56072663793.573723</v>
-      </c>
-      <c r="V14">
-        <v>3.4607600751235389E-2</v>
-      </c>
-      <c r="W14">
-        <v>0.13246039834856399</v>
-      </c>
-      <c r="X14">
-        <v>20.7412116291523</v>
-      </c>
-      <c r="Z14">
-        <v>79.126327972499098</v>
-      </c>
-      <c r="AA14">
-        <v>0.15430144547848201</v>
-      </c>
-      <c r="AD14">
-        <v>9.2368426370194889</v>
-      </c>
-      <c r="AE14">
-        <v>36.615610020152666</v>
-      </c>
-      <c r="AF14">
-        <v>25.264914637905171</v>
-      </c>
-      <c r="AG14">
-        <v>27.556785921536942</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="3">
-        <v>2012</v>
-      </c>
-      <c r="C15">
-        <v>274543305511.61057</v>
-      </c>
-      <c r="D15">
-        <v>4.4354975937853709</v>
-      </c>
-      <c r="E15">
-        <v>74324950448.238876</v>
-      </c>
-      <c r="F15">
-        <v>8.6296671918287444</v>
-      </c>
-      <c r="G15">
-        <v>3125729</v>
-      </c>
-      <c r="H15" s="53">
-        <v>3.72</v>
-      </c>
-      <c r="Q15">
-        <v>48.682609558105497</v>
-      </c>
-      <c r="S15">
-        <v>19.116821980066192</v>
-      </c>
-      <c r="T15">
-        <v>0.31910712270446595</v>
-      </c>
-      <c r="U15">
-        <v>56251595657.629143</v>
-      </c>
-      <c r="V15">
-        <v>3.3272726533169004E-2</v>
-      </c>
-      <c r="W15">
-        <v>0.12955873329242601</v>
-      </c>
-      <c r="X15">
-        <v>20.3739028359523</v>
-      </c>
-      <c r="Z15">
-        <v>79.496505082303997</v>
-      </c>
-      <c r="AA15">
-        <v>0.14329419862700701</v>
-      </c>
-      <c r="AD15">
-        <v>8.8578668846884447</v>
-      </c>
-      <c r="AE15">
-        <v>37.306048070547945</v>
-      </c>
-      <c r="AF15">
-        <v>26.429988298955582</v>
-      </c>
-      <c r="AG15">
-        <v>24.226259963852854</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" s="3">
-        <v>2013</v>
-      </c>
-      <c r="C16">
-        <v>287769788882.22137</v>
-      </c>
-      <c r="D16">
-        <v>4.8176309912067552</v>
-      </c>
-      <c r="E16">
-        <v>78902551233.793396</v>
-      </c>
-      <c r="F16">
-        <v>6.1589019003012169</v>
-      </c>
-      <c r="G16">
-        <v>3179345</v>
-      </c>
-      <c r="H16" s="53">
-        <v>3.86</v>
-      </c>
-      <c r="Q16">
-        <v>50.001869201660199</v>
-      </c>
-      <c r="S16">
-        <v>17.638409614875453</v>
-      </c>
-      <c r="T16">
-        <v>1.6712764155420388</v>
-      </c>
-      <c r="U16">
-        <v>57191715309.221169</v>
-      </c>
-      <c r="V16">
-        <v>3.4375216793813404E-2</v>
-      </c>
-      <c r="W16">
-        <v>0.12679854020966699</v>
-      </c>
-      <c r="X16">
-        <v>19.685489766741199</v>
-      </c>
-      <c r="Z16">
-        <v>80.187678894668295</v>
-      </c>
-      <c r="AA16">
-        <v>0.119459449682427</v>
-      </c>
-      <c r="AD16">
-        <v>9.7442177273746502</v>
-      </c>
-      <c r="AE16">
-        <v>37.333460129295503</v>
-      </c>
-      <c r="AF16">
-        <v>27.548215593668829</v>
-      </c>
-      <c r="AG16">
-        <v>23.113812627266899</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="3">
-        <v>2014</v>
-      </c>
-      <c r="C17">
-        <v>299095084828.97827</v>
-      </c>
-      <c r="D17">
-        <v>3.9355402770900696</v>
-      </c>
-      <c r="E17">
-        <v>82232429581.946793</v>
-      </c>
-      <c r="F17">
-        <v>4.2202416729045353</v>
-      </c>
-      <c r="G17">
-        <v>3266959</v>
-      </c>
-      <c r="H17" s="53">
-        <v>3.74</v>
-      </c>
-      <c r="Q17">
-        <v>51.152580261230497</v>
-      </c>
-      <c r="S17">
-        <v>17.999768892128522</v>
-      </c>
-      <c r="T17">
-        <v>2.6831203913080088</v>
-      </c>
-      <c r="U17">
-        <v>58726237884.821701</v>
-      </c>
-      <c r="V17">
-        <v>3.4540851073536168E-2</v>
-      </c>
-      <c r="W17">
-        <v>0.124092213197688</v>
-      </c>
-      <c r="X17">
-        <v>17.5887805852729</v>
-      </c>
-      <c r="Z17">
-        <v>82.287159069072601</v>
-      </c>
-      <c r="AA17">
-        <v>0.10487946932588101</v>
-      </c>
-      <c r="AD17">
-        <v>9.6310320219758019</v>
-      </c>
-      <c r="AE17">
-        <v>37.584381318964205</v>
-      </c>
-      <c r="AF17">
-        <v>28.128209222306971</v>
-      </c>
-      <c r="AG17">
-        <v>23.439752408773177</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="3">
-        <v>2015</v>
-      </c>
-      <c r="C18">
-        <v>307998545269.39795</v>
-      </c>
-      <c r="D18">
-        <v>2.9767993163480639</v>
-      </c>
-      <c r="E18">
-        <v>83844198352.517593</v>
-      </c>
-      <c r="F18">
-        <v>1.9600159921878912</v>
-      </c>
-      <c r="G18">
-        <v>3360400</v>
-      </c>
-      <c r="H18" s="53">
-        <v>3.79</v>
-      </c>
-      <c r="Q18">
-        <v>52.041000366210902</v>
-      </c>
-      <c r="S18">
-        <v>18.089329854873405</v>
-      </c>
-      <c r="T18">
-        <v>-5.1278017991461269</v>
-      </c>
-      <c r="U18">
-        <v>55714872801.992981</v>
-      </c>
-      <c r="V18">
-        <v>3.2613513802648333E-2</v>
-      </c>
-      <c r="W18">
-        <v>0.12145966005548101</v>
-      </c>
-      <c r="X18">
-        <v>17.2904642702552</v>
-      </c>
-      <c r="Z18">
-        <v>82.588076069689293</v>
-      </c>
-      <c r="AA18">
-        <v>3.4391157293545603E-2</v>
-      </c>
-      <c r="AD18">
-        <v>10.19090831587924</v>
-      </c>
-      <c r="AE18">
-        <v>37.158080606153213</v>
-      </c>
-      <c r="AF18">
-        <v>27.222270897150295</v>
-      </c>
-      <c r="AG18">
-        <v>27.297818059101541</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="3">
-        <v>2016</v>
-      </c>
-      <c r="C19">
-        <v>319541032495.04486</v>
-      </c>
-      <c r="D19">
-        <v>3.7475784879279246</v>
-      </c>
-      <c r="E19">
-        <v>84290655174.294907</v>
-      </c>
-      <c r="F19">
-        <v>0.53248385761912687</v>
-      </c>
-      <c r="G19">
-        <v>3396546</v>
-      </c>
-      <c r="H19" s="53">
-        <v>4.08</v>
-      </c>
-      <c r="Q19">
-        <v>52.7865180969238</v>
-      </c>
-      <c r="S19">
-        <v>17.441961312599027</v>
-      </c>
-      <c r="T19">
-        <v>3.7010008068074569</v>
-      </c>
-      <c r="U19">
-        <v>57776880693.906494</v>
-      </c>
-      <c r="V19">
-        <v>3.1521289438126224E-2</v>
-      </c>
-      <c r="W19">
-        <v>0.11897925916280699</v>
-      </c>
-      <c r="X19">
-        <v>16.156803308709499</v>
-      </c>
-      <c r="Z19">
-        <v>83.724217432127702</v>
-      </c>
-      <c r="AA19">
-        <v>2.9353972319112E-2</v>
-      </c>
-      <c r="AD19">
-        <v>10.200372971650724</v>
-      </c>
-      <c r="AE19">
-        <v>36.336754045415525</v>
-      </c>
-      <c r="AF19">
-        <v>25.877029477577924</v>
-      </c>
-      <c r="AG19">
-        <v>26.253769658413212</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" s="3">
-        <v>2017</v>
-      </c>
-      <c r="C20">
-        <v>333846562289.74597</v>
-      </c>
-      <c r="D20">
-        <v>4.4768991584587638</v>
-      </c>
-      <c r="E20">
-        <v>88598330696.634109</v>
-      </c>
-      <c r="F20">
-        <v>5.1105018859230142</v>
-      </c>
-      <c r="G20">
-        <v>3388507</v>
-      </c>
-      <c r="H20" s="53">
-        <v>4.2</v>
-      </c>
-      <c r="Q20">
-        <v>54.232109069824197</v>
-      </c>
-      <c r="S20">
-        <v>18.545847537786003</v>
-      </c>
-      <c r="T20">
-        <v>10.406115334791167</v>
-      </c>
-      <c r="U20">
-        <v>63789209535.759094</v>
-      </c>
-      <c r="V20">
-        <v>3.0763583755226389E-2</v>
-      </c>
-      <c r="W20">
-        <v>0.117077595142899</v>
-      </c>
-      <c r="X20">
-        <v>15.8830026161212</v>
-      </c>
-      <c r="Z20">
-        <v>83.999919788735895</v>
-      </c>
-      <c r="AA20">
-        <v>4.52888881904618E-4</v>
-      </c>
-      <c r="AD20">
-        <v>10.140018759338188</v>
-      </c>
-      <c r="AE20">
-        <v>35.184722354653985</v>
-      </c>
-      <c r="AF20">
-        <v>25.115649681750725</v>
-      </c>
-      <c r="AG20">
-        <v>26.545597667222111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="3">
-        <v>2018</v>
-      </c>
-      <c r="C21">
-        <v>345370865382.86688</v>
-      </c>
-      <c r="D21">
-        <v>3.4519759658686979</v>
-      </c>
-      <c r="E21">
-        <v>84207444583.856125</v>
-      </c>
-      <c r="F21">
-        <v>-4.9559467749032819</v>
-      </c>
-      <c r="G21">
-        <v>3390276</v>
-      </c>
-      <c r="H21" s="53">
-        <v>3.613</v>
-      </c>
-      <c r="Q21">
-        <v>55.760608673095703</v>
-      </c>
-      <c r="S21">
-        <v>20.717845766781217</v>
-      </c>
-      <c r="T21">
-        <v>7.0287004412821261</v>
-      </c>
-      <c r="U21">
-        <v>68272761987.889374</v>
-      </c>
-      <c r="V21">
-        <v>3.0117148236328394E-2</v>
-      </c>
-      <c r="W21">
-        <v>0.115089283007242</v>
-      </c>
-      <c r="X21">
-        <v>16.038846154906299</v>
-      </c>
-      <c r="Z21">
-        <v>83.846064562086497</v>
-      </c>
-      <c r="AA21">
-        <v>1.8876715293803699E-4</v>
-      </c>
-      <c r="AD21">
-        <v>9.9398348941138064</v>
-      </c>
-      <c r="AE21">
-        <v>34.614491407338598</v>
-      </c>
-      <c r="AF21">
-        <v>22.351805620065026</v>
-      </c>
-      <c r="AG21">
-        <v>29.700268952184881</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="3">
-        <v>2019</v>
-      </c>
-      <c r="C22">
-        <v>349888458531.08569</v>
-      </c>
-      <c r="D22">
-        <v>1.3080411815312658</v>
-      </c>
-      <c r="E22">
-        <v>86300365501.063766</v>
-      </c>
-      <c r="F22">
-        <v>2.4854345450697792</v>
-      </c>
-      <c r="G22">
-        <v>3454121</v>
-      </c>
-      <c r="H22" s="53">
-        <v>3.1</v>
-      </c>
-      <c r="Q22">
-        <v>57.249900817871101</v>
-      </c>
-      <c r="S22">
-        <v>19.40403130191034</v>
-      </c>
-      <c r="T22">
-        <v>-1.4550979032228923</v>
-      </c>
-      <c r="U22">
-        <v>67279326459.731239</v>
-      </c>
-      <c r="V22">
-        <v>3.2252130199608528E-2</v>
-      </c>
-      <c r="W22">
-        <v>0.113041897035994</v>
-      </c>
-      <c r="X22">
-        <v>14.9655328914049</v>
-      </c>
-      <c r="Z22">
-        <v>84.921455267899702</v>
-      </c>
-      <c r="AA22">
-        <v>1.6926616042902101E-4</v>
-      </c>
-      <c r="AD22">
-        <v>10.253396494246401</v>
-      </c>
-      <c r="AE22">
-        <v>35.845393881281687</v>
-      </c>
-      <c r="AF22">
-        <v>22.799478885505962</v>
-      </c>
-      <c r="AG22">
-        <v>29.367995967723893</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="3">
-        <v>2020</v>
-      </c>
-      <c r="C23">
-        <v>336541232520.5025</v>
-      </c>
-      <c r="D23">
-        <v>-3.8147088551071278</v>
-      </c>
-      <c r="E23">
-        <v>74186532831.451279</v>
-      </c>
-      <c r="F23">
-        <v>-14.036826610500484</v>
-      </c>
-      <c r="G23">
-        <v>3431193</v>
-      </c>
-      <c r="H23" s="53">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="Q23">
-        <v>58.2861518859863</v>
-      </c>
-      <c r="S23">
-        <v>19.653984525036179</v>
-      </c>
-      <c r="T23">
-        <v>7.5307063016974496</v>
-      </c>
-      <c r="U23">
-        <v>72345934937.173828</v>
-      </c>
-      <c r="V23">
-        <v>3.281725211869508E-2</v>
-      </c>
-      <c r="W23">
-        <v>0.108162685533748</v>
-      </c>
-      <c r="X23">
-        <v>14.8295407728436</v>
-      </c>
-      <c r="Z23">
-        <v>85.0622965416227</v>
-      </c>
-      <c r="AA23">
-        <v>2.4207226855628999E-4</v>
-      </c>
-      <c r="AD23">
-        <v>12.190147791383446</v>
-      </c>
-      <c r="AE23">
-        <v>32.147432325908682</v>
-      </c>
-      <c r="AF23">
-        <v>20.999459350147131</v>
-      </c>
-      <c r="AG23">
-        <v>31.279400415186071</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="3">
-        <v>2021</v>
-      </c>
-      <c r="C24">
-        <v>369376902514.86536</v>
-      </c>
-      <c r="D24">
-        <v>9.7568044629903028</v>
-      </c>
-      <c r="E24">
-        <v>91394322913.825394</v>
-      </c>
-      <c r="F24">
-        <v>23.19530166138037</v>
-      </c>
-      <c r="G24">
-        <v>3385810</v>
-      </c>
-      <c r="H24" s="53">
-        <v>4.6399999999999997</v>
-      </c>
-      <c r="Q24">
-        <v>61.837471008300803</v>
-      </c>
-      <c r="S24">
-        <v>20.633068003561824</v>
-      </c>
-      <c r="T24">
-        <v>13.303540009852924</v>
-      </c>
-      <c r="U24">
-        <v>81970505337.042892</v>
-      </c>
-      <c r="V24">
-        <v>3.0551368665513827E-2</v>
-      </c>
-      <c r="W24">
-        <v>0.107777556138585</v>
-      </c>
-      <c r="X24">
-        <v>14.4449638584304</v>
-      </c>
-      <c r="Z24">
-        <v>85.447258585431001</v>
-      </c>
-      <c r="AA24">
-        <v>1.80989109199595E-4</v>
-      </c>
-      <c r="AD24">
-        <v>10.532697743092175</v>
-      </c>
-      <c r="AE24">
-        <v>28.780240455600087</v>
-      </c>
-      <c r="AF24">
-        <v>22.078228221894115</v>
-      </c>
-      <c r="AG24">
-        <v>35.785344863952751</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="3">
-        <v>2022</v>
-      </c>
-      <c r="C25">
-        <v>384550906479.00623</v>
-      </c>
-      <c r="D25">
-        <v>4.1080002189715117</v>
-      </c>
-      <c r="E25">
-        <v>95674867710.435883</v>
-      </c>
-      <c r="F25">
-        <v>4.6836003157948483</v>
-      </c>
-      <c r="G25">
-        <v>3459003</v>
-      </c>
-      <c r="H25" s="53">
-        <v>3.5910000000000002</v>
-      </c>
-      <c r="Q25">
-        <v>63.086940765380902</v>
-      </c>
-      <c r="S25">
-        <v>19.655537649937781</v>
-      </c>
-      <c r="T25">
-        <v>2.6997624563978491</v>
-      </c>
-      <c r="U25">
-        <v>84183514265.451965</v>
-      </c>
-      <c r="V25">
-        <v>2.597731637364643E-2</v>
-      </c>
-      <c r="W25">
-        <v>9.0952445633474793E-2</v>
-      </c>
-      <c r="X25">
-        <v>14.5645681583865</v>
-      </c>
-      <c r="Z25">
-        <v>85.344449477412397</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD25">
-        <v>9.1289494952629333</v>
-      </c>
-      <c r="AE25">
-        <v>28.099108159151914</v>
-      </c>
-      <c r="AF25">
-        <v>20.338964403941983</v>
-      </c>
-      <c r="AG25">
-        <v>39.774395154749833</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="3">
-        <v>2023</v>
-      </c>
-      <c r="C26">
-        <v>391555143381.88489</v>
-      </c>
-      <c r="D26">
-        <v>1.8214069411538532</v>
-      </c>
-      <c r="E26">
-        <v>94809012056.079865</v>
-      </c>
-      <c r="F26">
-        <v>-0.90499801575536765</v>
-      </c>
-      <c r="G26">
-        <v>3622441</v>
-      </c>
-      <c r="H26" s="53">
-        <v>3.444</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>169</v>
-      </c>
-      <c r="S26">
-        <v>16.975559443779353</v>
-      </c>
-      <c r="T26">
-        <v>-4.2302587923025925</v>
-      </c>
-      <c r="U26">
-        <v>80622333751.568375</v>
-      </c>
-      <c r="V26">
-        <v>2.8849802007551339E-2</v>
-      </c>
-      <c r="W26">
-        <v>7.9580186024164501E-2</v>
-      </c>
-      <c r="X26">
-        <v>13.8432992197459</v>
-      </c>
-      <c r="Z26">
-        <v>86.077120594229896</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD26">
-        <v>9.8421032695316715</v>
-      </c>
-      <c r="AE26">
-        <v>31.513116296958909</v>
-      </c>
-      <c r="AF26">
-        <v>21.87302410554809</v>
-      </c>
-      <c r="AG26">
-        <v>37.158805824026295</v>
-      </c>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>75</v>
-      </c>
-      <c r="B27" s="3">
-        <v>2024</v>
-      </c>
-      <c r="C27">
-        <v>408736675576.89142</v>
-      </c>
-      <c r="D27">
-        <v>4.3880236246186541</v>
-      </c>
-      <c r="E27">
-        <v>97592930009.273911</v>
-      </c>
-      <c r="F27">
-        <v>2.9363431733128351</v>
-      </c>
-      <c r="G27">
-        <v>3689424</v>
-      </c>
-      <c r="H27" s="53">
-        <v>2.7370000000000001</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>169</v>
-      </c>
-      <c r="S27">
-        <v>16.332704934853503</v>
-      </c>
-      <c r="T27">
-        <v>4.2628399445695493</v>
-      </c>
-      <c r="U27">
-        <v>84059134798.974411</v>
-      </c>
-      <c r="V27">
-        <v>2.7439170694473516E-2</v>
-      </c>
-      <c r="W27">
-        <v>9.7983733027354095E-2</v>
-      </c>
-      <c r="X27">
-        <v>14.162557810979401</v>
-      </c>
-      <c r="Z27">
-        <v>85.739458455993301</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD27">
-        <v>10.05318763287927</v>
-      </c>
-      <c r="AE27">
-        <v>30.684280484260235</v>
-      </c>
-      <c r="AF27">
-        <v>21.037456033494557</v>
-      </c>
-      <c r="AG27">
-        <v>36.012331849548822</v>
-      </c>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.45">
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8A5EBE0-77D1-4DEE-BD25-B861D3CF253E}">
-  <dimension ref="A1:AJ29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="3" max="3" width="11.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.06640625" style="3"/>
-    <col min="5" max="5" width="3.33203125" style="28" customWidth="1"/>
-    <col min="6" max="6" width="9.06640625" style="3"/>
-    <col min="8" max="8" width="5.06640625" style="29" customWidth="1"/>
-    <col min="11" max="11" width="17.53125" style="6" customWidth="1"/>
-    <col min="12" max="13" width="9.06640625" style="6"/>
-    <col min="14" max="14" width="12.19921875" style="6" customWidth="1"/>
-    <col min="15" max="15" width="12.19921875" style="9" customWidth="1"/>
-    <col min="16" max="16" width="9.06640625" style="6"/>
-    <col min="17" max="17" width="14.265625" style="7" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.19921875" style="31" customWidth="1"/>
-    <col min="19" max="19" width="13.33203125" customWidth="1"/>
-    <col min="20" max="20" width="13.33203125" style="25" customWidth="1"/>
-    <col min="21" max="21" width="4.46484375" style="29" customWidth="1"/>
-    <col min="22" max="22" width="13.33203125" customWidth="1"/>
-    <col min="23" max="23" width="16.06640625" customWidth="1"/>
-    <col min="24" max="24" width="13.46484375" customWidth="1"/>
-    <col min="29" max="29" width="3.73046875" style="29" customWidth="1"/>
-    <col min="31" max="31" width="9.06640625" style="25"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:36" s="2" customFormat="1" ht="151.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:36" s="2" customFormat="1" ht="151.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
@@ -10726,7 +8969,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:36" s="23" customFormat="1" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:36" s="23" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="C2" s="23" t="s">
         <v>106</v>
       </c>
@@ -10764,15 +9007,15 @@
         <v>152</v>
       </c>
       <c r="U2" s="32"/>
-      <c r="V2" s="41" t="s">
+      <c r="V2" s="59" t="s">
         <v>155</v>
       </c>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="41"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
       <c r="AC2" s="33"/>
       <c r="AD2" s="23" t="s">
         <v>148</v>
@@ -10780,7 +9023,7 @@
       <c r="AE2" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="AG2" s="49" t="s">
+      <c r="AG2" s="48" t="s">
         <v>165</v>
       </c>
       <c r="AH2" s="23" t="s">
@@ -10793,132 +9036,132 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>2000</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2001</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2002</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2003</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>2004</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>2005</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>2006</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>2007</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>2008</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>2009</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>2010</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>2011</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>2012</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>2013</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>2014</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>2015</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>2016</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>2017</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>2018</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>2019</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>2020</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>2021</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>2022</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>2023</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>2024</v>
       </c>
     </row>
-    <row r="29" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>113</v>
       </c>
@@ -10968,16 +9211,2789 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1524E039-9D98-4AD9-9E87-88901946F8BA}">
+  <dimension ref="A1:AG29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="9" style="3"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="52"/>
+    <col min="9" max="9" width="17.5703125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="19" style="6" customWidth="1"/>
+    <col min="11" max="11" width="9" style="42"/>
+    <col min="12" max="12" width="12.140625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" style="9" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="9" style="42"/>
+    <col min="16" max="16" width="9" style="49"/>
+    <col min="17" max="17" width="15.5703125" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" style="25" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="25" customWidth="1"/>
+    <col min="28" max="28" width="12" style="25" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.5703125" customWidth="1"/>
+    <col min="30" max="33" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" s="2" customFormat="1" ht="151.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K1" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="R1" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y1" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB1" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" s="56" customFormat="1" ht="113.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="J2" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="K2" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="L2" s="55" t="s">
+        <v>172</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="N2" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="R2" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y2" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB2" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="AD2" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE2" s="54" t="s">
+        <v>166</v>
+      </c>
+      <c r="AF2" s="54" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG2" s="54" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C3" s="60">
+        <v>140533304238.72125</v>
+      </c>
+      <c r="D3">
+        <v>9.0383163255516337</v>
+      </c>
+      <c r="E3" s="60">
+        <v>43703162220.646263</v>
+      </c>
+      <c r="F3">
+        <v>11.414764762166143</v>
+      </c>
+      <c r="G3">
+        <v>2138100</v>
+      </c>
+      <c r="H3" s="52">
+        <v>3.7</v>
+      </c>
+      <c r="I3" s="6">
+        <f>100-H3</f>
+        <v>96.3</v>
+      </c>
+      <c r="J3" s="6">
+        <f>(I3/100)*G3</f>
+        <v>2058990.2999999998</v>
+      </c>
+      <c r="K3" s="62"/>
+      <c r="L3" s="61">
+        <f>C3/J3</f>
+        <v>68253.504758483454</v>
+      </c>
+      <c r="M3" s="63"/>
+      <c r="N3" s="61">
+        <f>E3/J3</f>
+        <v>21225.530892810068</v>
+      </c>
+      <c r="O3" s="62"/>
+      <c r="Q3" t="s">
+        <v>169</v>
+      </c>
+      <c r="R3" s="46"/>
+      <c r="S3">
+        <v>25.861486037755899</v>
+      </c>
+      <c r="T3">
+        <v>15.146298038161788</v>
+      </c>
+      <c r="U3">
+        <v>29918062298.838032</v>
+      </c>
+      <c r="V3">
+        <v>9.2131732680321002E-2</v>
+      </c>
+      <c r="W3">
+        <v>0.17689908365402099</v>
+      </c>
+      <c r="X3">
+        <v>27.293652478865699</v>
+      </c>
+      <c r="Y3" s="46"/>
+      <c r="Z3">
+        <v>72.529399958696104</v>
+      </c>
+      <c r="AA3">
+        <v>3.26034372238966E-4</v>
+      </c>
+      <c r="AB3" s="46"/>
+      <c r="AD3">
+        <v>10.504164644115525</v>
+      </c>
+      <c r="AE3">
+        <v>41.855216732958041</v>
+      </c>
+      <c r="AF3">
+        <v>32.326344362576407</v>
+      </c>
+      <c r="AG3">
+        <v>12.337260101284532</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2001</v>
+      </c>
+      <c r="C4" s="60">
+        <v>139028385430.87299</v>
+      </c>
+      <c r="D4">
+        <v>-1.0708627510044835</v>
+      </c>
+      <c r="E4" s="60">
+        <v>41427454403.287689</v>
+      </c>
+      <c r="F4">
+        <v>-5.2071925730891024</v>
+      </c>
+      <c r="G4">
+        <v>2205923</v>
+      </c>
+      <c r="H4" s="52">
+        <v>3.76</v>
+      </c>
+      <c r="I4" s="6">
+        <f t="shared" ref="I4:I27" si="0">100-H4</f>
+        <v>96.24</v>
+      </c>
+      <c r="J4" s="6">
+        <f t="shared" ref="J4:J27" si="1">(I4/100)*G4</f>
+        <v>2122980.2952000001</v>
+      </c>
+      <c r="K4" s="42">
+        <f>((J4-J3)/J3)</f>
+        <v>3.1078337377305879E-2</v>
+      </c>
+      <c r="L4" s="61">
+        <f t="shared" ref="L4:L27" si="2">C4/J4</f>
+        <v>65487.364977061887</v>
+      </c>
+      <c r="M4" s="9">
+        <f>(L4-L3)/L3</f>
+        <v>-4.0527439451052576E-2</v>
+      </c>
+      <c r="N4" s="61">
+        <f t="shared" ref="N4:N27" si="3">E4/J4</f>
+        <v>19513.819556853177</v>
+      </c>
+      <c r="O4" s="42">
+        <f>(N4-N3)/N3</f>
+        <v>-8.0643982221274613E-2</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>169</v>
+      </c>
+      <c r="R4" s="46"/>
+      <c r="S4">
+        <v>23.394697847414562</v>
+      </c>
+      <c r="T4">
+        <v>-11.605048125430017</v>
+      </c>
+      <c r="U4">
+        <v>26446056770.861744</v>
+      </c>
+      <c r="V4">
+        <v>8.2356655909540694E-2</v>
+      </c>
+      <c r="W4">
+        <v>0.173741005150197</v>
+      </c>
+      <c r="X4">
+        <v>26.157941891234099</v>
+      </c>
+      <c r="Y4" s="25">
+        <f>X4-X3</f>
+        <v>-1.1357105876315998</v>
+      </c>
+      <c r="Z4">
+        <v>73.668317103615706</v>
+      </c>
+      <c r="AA4">
+        <v>4.0237915923044699E-4</v>
+      </c>
+      <c r="AB4" s="25">
+        <f>AA4-AA3</f>
+        <v>7.6344786991480989E-5</v>
+      </c>
+      <c r="AD4">
+        <v>11.609926556509718</v>
+      </c>
+      <c r="AE4">
+        <v>46.244971582292017</v>
+      </c>
+      <c r="AF4">
+        <v>30.887040232314138</v>
+      </c>
+      <c r="AG4">
+        <v>16.496255724564534</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2002</v>
+      </c>
+      <c r="C5" s="60">
+        <v>144482970559.8894</v>
+      </c>
+      <c r="D5">
+        <v>3.923360767020128</v>
+      </c>
+      <c r="E5" s="60">
+        <v>37635189933.264236</v>
+      </c>
+      <c r="F5">
+        <v>-9.1539886402542265</v>
+      </c>
+      <c r="G5">
+        <v>2200772</v>
+      </c>
+      <c r="H5" s="52">
+        <v>5.65</v>
+      </c>
+      <c r="I5" s="6">
+        <f t="shared" si="0"/>
+        <v>94.35</v>
+      </c>
+      <c r="J5" s="6">
+        <f t="shared" si="1"/>
+        <v>2076428.3819999998</v>
+      </c>
+      <c r="K5" s="42">
+        <f t="shared" ref="K5:K27" si="4">((J5-J4)/J4)</f>
+        <v>-2.1927623777409942E-2</v>
+      </c>
+      <c r="L5" s="61">
+        <f t="shared" si="2"/>
+        <v>69582.448309979532</v>
+      </c>
+      <c r="M5" s="9">
+        <f t="shared" ref="M5:M27" si="5">(L5-L4)/L4</f>
+        <v>6.253241880097056E-2</v>
+      </c>
+      <c r="N5" s="61">
+        <f t="shared" si="3"/>
+        <v>18124.964125665781</v>
+      </c>
+      <c r="O5" s="42">
+        <f t="shared" ref="O5:O27" si="6">(N5-N4)/N4</f>
+        <v>-7.1172915540240064E-2</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>169</v>
+      </c>
+      <c r="R5" s="46"/>
+      <c r="S5">
+        <v>24.737640322972926</v>
+      </c>
+      <c r="T5">
+        <v>8.4686746225800107</v>
+      </c>
+      <c r="U5">
+        <v>28685687269.288815</v>
+      </c>
+      <c r="V5">
+        <v>7.1032800014001363E-2</v>
+      </c>
+      <c r="W5">
+        <v>0.16944763175838501</v>
+      </c>
+      <c r="X5">
+        <v>25.389889592307298</v>
+      </c>
+      <c r="Y5" s="25">
+        <f t="shared" ref="Y5:Y27" si="7">X5-X4</f>
+        <v>-0.7680522989268006</v>
+      </c>
+      <c r="Z5">
+        <v>74.440662775934399</v>
+      </c>
+      <c r="AA5">
+        <v>4.3398819080536202E-4</v>
+      </c>
+      <c r="AB5" s="25">
+        <f t="shared" ref="AB5:AB27" si="8">AA5-AA4</f>
+        <v>3.1609031574915034E-5</v>
+      </c>
+      <c r="AD5">
+        <v>11.84032888729563</v>
+      </c>
+      <c r="AE5">
+        <v>46.182484892705467</v>
+      </c>
+      <c r="AF5">
+        <v>26.751423220905973</v>
+      </c>
+      <c r="AG5">
+        <v>18.426222147387328</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2003</v>
+      </c>
+      <c r="C6" s="60">
+        <v>151054425108.65015</v>
+      </c>
+      <c r="D6">
+        <v>4.5482554264322914</v>
+      </c>
+      <c r="E6" s="60">
+        <v>35694579310.094017</v>
+      </c>
+      <c r="F6">
+        <v>-5.1563726039681654</v>
+      </c>
+      <c r="G6">
+        <v>2176377</v>
+      </c>
+      <c r="H6" s="52">
+        <v>5.93</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" si="0"/>
+        <v>94.07</v>
+      </c>
+      <c r="J6" s="6">
+        <f t="shared" si="1"/>
+        <v>2047317.8439</v>
+      </c>
+      <c r="K6" s="42">
+        <f t="shared" si="4"/>
+        <v>-1.4019524271750093E-2</v>
+      </c>
+      <c r="L6" s="61">
+        <f t="shared" si="2"/>
+        <v>73781.618989312294</v>
+      </c>
+      <c r="M6" s="9">
+        <f t="shared" si="5"/>
+        <v>6.034813061802706E-2</v>
+      </c>
+      <c r="N6" s="61">
+        <f t="shared" si="3"/>
+        <v>17434.801057611206</v>
+      </c>
+      <c r="O6" s="42">
+        <f t="shared" si="6"/>
+        <v>-3.8078037742280128E-2</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>169</v>
+      </c>
+      <c r="R6" s="46"/>
+      <c r="S6">
+        <v>24.765412693196893</v>
+      </c>
+      <c r="T6">
+        <v>2.9963638945377227</v>
+      </c>
+      <c r="U6">
+        <v>29545214845.525787</v>
+      </c>
+      <c r="V6">
+        <v>6.1134072311026647E-2</v>
+      </c>
+      <c r="W6">
+        <v>0.16459654177274699</v>
+      </c>
+      <c r="X6">
+        <v>24.785305691086901</v>
+      </c>
+      <c r="Y6" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.60458390122039773</v>
+      </c>
+      <c r="Z6">
+        <v>75.050049199261395</v>
+      </c>
+      <c r="AA6">
+        <v>5.9371726127004001E-4</v>
+      </c>
+      <c r="AB6" s="25">
+        <f t="shared" si="8"/>
+        <v>1.5972907046467799E-4</v>
+      </c>
+      <c r="AD6">
+        <v>11.4140839970397</v>
+      </c>
+      <c r="AE6">
+        <v>45.535361064297177</v>
+      </c>
+      <c r="AF6">
+        <v>24.766294434624459</v>
+      </c>
+      <c r="AG6">
+        <v>27.953848478026121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2004</v>
+      </c>
+      <c r="C7" s="60">
+        <v>166069208808.39377</v>
+      </c>
+      <c r="D7">
+        <v>9.9399826843495731</v>
+      </c>
+      <c r="E7" s="60">
+        <v>39369010601.349266</v>
+      </c>
+      <c r="F7">
+        <v>10.294087680187801</v>
+      </c>
+      <c r="G7">
+        <v>2211220</v>
+      </c>
+      <c r="H7" s="52">
+        <v>5.84</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" si="0"/>
+        <v>94.16</v>
+      </c>
+      <c r="J7" s="6">
+        <f t="shared" si="1"/>
+        <v>2082084.7520000001</v>
+      </c>
+      <c r="K7" s="42">
+        <f t="shared" si="4"/>
+        <v>1.6981685674058087E-2</v>
+      </c>
+      <c r="L7" s="61">
+        <f t="shared" si="2"/>
+        <v>79761.022527479596</v>
+      </c>
+      <c r="M7" s="9">
+        <f t="shared" si="5"/>
+        <v>8.1041912878510494E-2</v>
+      </c>
+      <c r="N7" s="61">
+        <f t="shared" si="3"/>
+        <v>18908.457287116842</v>
+      </c>
+      <c r="O7" s="42">
+        <f t="shared" si="6"/>
+        <v>8.4523833947752855E-2</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>169</v>
+      </c>
+      <c r="R7" s="46"/>
+      <c r="S7">
+        <v>27.119367597064286</v>
+      </c>
+      <c r="T7">
+        <v>13.8458129716023</v>
+      </c>
+      <c r="U7">
+        <v>33635990035.095367</v>
+      </c>
+      <c r="V7">
+        <v>5.5648989626246571E-2</v>
+      </c>
+      <c r="W7">
+        <v>0.15970081754349399</v>
+      </c>
+      <c r="X7">
+        <v>24.4105337316422</v>
+      </c>
+      <c r="Y7" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.37477195944470054</v>
+      </c>
+      <c r="Z7">
+        <v>75.429717492610806</v>
+      </c>
+      <c r="AA7">
+        <v>5.5564498338846495E-4</v>
+      </c>
+      <c r="AB7" s="25">
+        <f t="shared" si="8"/>
+        <v>-3.8072277881575061E-5</v>
+      </c>
+      <c r="AD7">
+        <v>10.318670184588006</v>
+      </c>
+      <c r="AE7">
+        <v>41.998426193084512</v>
+      </c>
+      <c r="AF7">
+        <v>24.281423420921346</v>
+      </c>
+      <c r="AG7">
+        <v>26.379678346782697</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2005</v>
+      </c>
+      <c r="C8" s="60">
+        <v>178302402123.90665</v>
+      </c>
+      <c r="D8">
+        <v>7.366322392507584</v>
+      </c>
+      <c r="E8" s="60">
+        <v>40801992980.92485</v>
+      </c>
+      <c r="F8">
+        <v>3.6398739965450631</v>
+      </c>
+      <c r="G8">
+        <v>2301785</v>
+      </c>
+      <c r="H8" s="52">
+        <v>5.59</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="0"/>
+        <v>94.41</v>
+      </c>
+      <c r="J8" s="6">
+        <f t="shared" si="1"/>
+        <v>2173115.2185</v>
+      </c>
+      <c r="K8" s="42">
+        <f t="shared" si="4"/>
+        <v>4.3720826643852136E-2</v>
+      </c>
+      <c r="L8" s="61">
+        <f t="shared" si="2"/>
+        <v>82049.21699779015</v>
+      </c>
+      <c r="M8" s="9">
+        <f t="shared" si="5"/>
+        <v>2.8688128584638147E-2</v>
+      </c>
+      <c r="N8" s="61">
+        <f t="shared" si="3"/>
+        <v>18775.807482996028</v>
+      </c>
+      <c r="O8" s="42">
+        <f t="shared" si="6"/>
+        <v>-7.0153689487504793E-3</v>
+      </c>
+      <c r="Q8">
+        <v>38.256099700927699</v>
+      </c>
+      <c r="R8" s="46"/>
+      <c r="S8">
+        <v>27.076761798207059</v>
+      </c>
+      <c r="T8">
+        <v>9.5096402529214856</v>
+      </c>
+      <c r="U8">
+        <v>36834651682.94146</v>
+      </c>
+      <c r="V8">
+        <v>5.5048114214259862E-2</v>
+      </c>
+      <c r="W8">
+        <v>0.155212233759282</v>
+      </c>
+      <c r="X8">
+        <v>23.882954799438199</v>
+      </c>
+      <c r="Y8" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.52757893220400121</v>
+      </c>
+      <c r="Z8">
+        <v>75.961878955612505</v>
+      </c>
+      <c r="AA8">
+        <v>5.4706140442952399E-4</v>
+      </c>
+      <c r="AB8" s="25">
+        <f t="shared" si="8"/>
+        <v>-8.5835789589409515E-6</v>
+      </c>
+      <c r="AD8">
+        <v>9.8971432332187881</v>
+      </c>
+      <c r="AE8">
+        <v>39.847877286424129</v>
+      </c>
+      <c r="AF8">
+        <v>23.187995656323011</v>
+      </c>
+      <c r="AG8">
+        <v>29.88882255327351</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2006</v>
+      </c>
+      <c r="C9" s="60">
+        <v>194361682395.94128</v>
+      </c>
+      <c r="D9">
+        <v>9.0067660787175754</v>
+      </c>
+      <c r="E9" s="60">
+        <v>44652955830.742096</v>
+      </c>
+      <c r="F9">
+        <v>9.4381734039746306</v>
+      </c>
+      <c r="G9">
+        <v>2426201</v>
+      </c>
+      <c r="H9" s="52">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="0"/>
+        <v>95.52</v>
+      </c>
+      <c r="J9" s="6">
+        <f t="shared" si="1"/>
+        <v>2317507.1952</v>
+      </c>
+      <c r="K9" s="42">
+        <f t="shared" si="4"/>
+        <v>6.6444694450976713E-2</v>
+      </c>
+      <c r="L9" s="61">
+        <f t="shared" si="2"/>
+        <v>83866.700737111605</v>
+      </c>
+      <c r="M9" s="9">
+        <f t="shared" si="5"/>
+        <v>2.2151140569329326E-2</v>
+      </c>
+      <c r="N9" s="61">
+        <f t="shared" si="3"/>
+        <v>19267.666535502845</v>
+      </c>
+      <c r="O9" s="42">
+        <f t="shared" si="6"/>
+        <v>2.6196426063287068E-2</v>
+      </c>
+      <c r="Q9">
+        <v>36.755790710449197</v>
+      </c>
+      <c r="R9" s="25">
+        <f>Q9-Q8</f>
+        <v>-1.5003089904785014</v>
+      </c>
+      <c r="S9">
+        <v>26.578005985802772</v>
+      </c>
+      <c r="T9">
+        <v>11.921913382779238</v>
+      </c>
+      <c r="U9">
+        <v>41226046951.430176</v>
+      </c>
+      <c r="V9">
+        <v>4.8865424451682515E-2</v>
+      </c>
+      <c r="W9">
+        <v>0.15069969562712299</v>
+      </c>
+      <c r="X9">
+        <v>23.2978195732057</v>
+      </c>
+      <c r="Y9" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.5851352262324987</v>
+      </c>
+      <c r="Z9">
+        <v>76.5515238251608</v>
+      </c>
+      <c r="AA9">
+        <v>3.65545459554034E-3</v>
+      </c>
+      <c r="AB9" s="25">
+        <f t="shared" si="8"/>
+        <v>3.1083931911108161E-3</v>
+      </c>
+      <c r="AD9">
+        <v>9.9069355027210513</v>
+      </c>
+      <c r="AE9">
+        <v>38.106096406316425</v>
+      </c>
+      <c r="AF9">
+        <v>23.086711145212458</v>
+      </c>
+      <c r="AG9">
+        <v>30.711834579105247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2007</v>
+      </c>
+      <c r="C10" s="60">
+        <v>211896059498.4816</v>
+      </c>
+      <c r="D10">
+        <v>9.0215195126889256</v>
+      </c>
+      <c r="E10" s="60">
+        <v>51576309712.14518</v>
+      </c>
+      <c r="F10">
+        <v>15.504805342889711</v>
+      </c>
+      <c r="G10">
+        <v>2530038</v>
+      </c>
+      <c r="H10" s="52">
+        <v>3.9</v>
+      </c>
+      <c r="I10" s="6">
+        <f t="shared" si="0"/>
+        <v>96.1</v>
+      </c>
+      <c r="J10" s="6">
+        <f t="shared" si="1"/>
+        <v>2431366.5179999997</v>
+      </c>
+      <c r="K10" s="42">
+        <f t="shared" si="4"/>
+        <v>4.9130083840008838E-2</v>
+      </c>
+      <c r="L10" s="61">
+        <f t="shared" si="2"/>
+        <v>87151.014842790406</v>
+      </c>
+      <c r="M10" s="9">
+        <f t="shared" si="5"/>
+        <v>3.9161122076016859E-2</v>
+      </c>
+      <c r="N10" s="61">
+        <f t="shared" si="3"/>
+        <v>21212.889677600302</v>
+      </c>
+      <c r="O10" s="42">
+        <f t="shared" si="6"/>
+        <v>0.10095789952110516</v>
+      </c>
+      <c r="Q10">
+        <v>37.784400939941399</v>
+      </c>
+      <c r="R10" s="25">
+        <f>Q10-Q9</f>
+        <v>1.0286102294922017</v>
+      </c>
+      <c r="S10">
+        <v>23.822651904527213</v>
+      </c>
+      <c r="T10">
+        <v>5.9408665704516324</v>
+      </c>
+      <c r="U10">
+        <v>43675231393.086388</v>
+      </c>
+      <c r="V10">
+        <v>4.286799737144735E-2</v>
+      </c>
+      <c r="W10">
+        <v>0.14645508484910399</v>
+      </c>
+      <c r="X10">
+        <v>23.590067003098699</v>
+      </c>
+      <c r="Y10" s="25">
+        <f t="shared" si="7"/>
+        <v>0.29224742989299912</v>
+      </c>
+      <c r="Z10">
+        <v>76.263477912052196</v>
+      </c>
+      <c r="AA10">
+        <v>6.8551812889980296E-3</v>
+      </c>
+      <c r="AB10" s="25">
+        <f t="shared" si="8"/>
+        <v>3.1997266934576897E-3</v>
+      </c>
+      <c r="AD10">
+        <v>9.1361273439883615</v>
+      </c>
+      <c r="AE10">
+        <v>36.765963470158894</v>
+      </c>
+      <c r="AF10">
+        <v>24.375682074209674</v>
+      </c>
+      <c r="AG10">
+        <v>31.270315543664491</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2008</v>
+      </c>
+      <c r="C11" s="60">
+        <v>215844707508.2283</v>
+      </c>
+      <c r="D11">
+        <v>1.8634834546203507</v>
+      </c>
+      <c r="E11" s="60">
+        <v>57123779390.104187</v>
+      </c>
+      <c r="F11">
+        <v>10.755848390317652</v>
+      </c>
+      <c r="G11">
+        <v>2737323</v>
+      </c>
+      <c r="H11" s="52">
+        <v>3.96</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="0"/>
+        <v>96.04</v>
+      </c>
+      <c r="J11" s="6">
+        <f t="shared" si="1"/>
+        <v>2628925.0092000002</v>
+      </c>
+      <c r="K11" s="42">
+        <f t="shared" si="4"/>
+        <v>8.1254097124981689E-2</v>
+      </c>
+      <c r="L11" s="61">
+        <f t="shared" si="2"/>
+        <v>82103.790238547474</v>
+      </c>
+      <c r="M11" s="9">
+        <f t="shared" si="5"/>
+        <v>-5.7913549410153149E-2</v>
+      </c>
+      <c r="N11" s="61">
+        <f t="shared" si="3"/>
+        <v>21728.949738086041</v>
+      </c>
+      <c r="O11" s="42">
+        <f t="shared" si="6"/>
+        <v>2.4327664374301224E-2</v>
+      </c>
+      <c r="Q11">
+        <v>40.407138824462898</v>
+      </c>
+      <c r="R11" s="25">
+        <f t="shared" ref="R11:R25" si="9">Q11-Q10</f>
+        <v>2.6227378845214986</v>
+      </c>
+      <c r="S11">
+        <v>20.585664973848445</v>
+      </c>
+      <c r="T11">
+        <v>-4.1884694683058541</v>
+      </c>
+      <c r="U11">
+        <v>41845907660.975029</v>
+      </c>
+      <c r="V11">
+        <v>4.1432188466446869E-2</v>
+      </c>
+      <c r="W11">
+        <v>0.14231124802675299</v>
+      </c>
+      <c r="X11">
+        <v>23.729672967526501</v>
+      </c>
+      <c r="Y11" s="25">
+        <f t="shared" si="7"/>
+        <v>0.13960596442780115</v>
+      </c>
+      <c r="Z11">
+        <v>76.128015784446703</v>
+      </c>
+      <c r="AA11">
+        <v>2.5386566425965599E-2</v>
+      </c>
+      <c r="AB11" s="25">
+        <f t="shared" si="8"/>
+        <v>1.853138513696757E-2</v>
+      </c>
+      <c r="AD11">
+        <v>10.113213911286202</v>
+      </c>
+      <c r="AE11">
+        <v>39.95092384654248</v>
+      </c>
+      <c r="AF11">
+        <v>27.978919594541324</v>
+      </c>
+      <c r="AG11">
+        <v>20.660826979180964</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2009</v>
+      </c>
+      <c r="C12" s="60">
+        <v>216120888113.03256</v>
+      </c>
+      <c r="D12">
+        <v>0.1279533827780881</v>
+      </c>
+      <c r="E12" s="60">
+        <v>60258141945.338493</v>
+      </c>
+      <c r="F12">
+        <v>5.4869663539406588</v>
+      </c>
+      <c r="G12">
+        <v>2837096</v>
+      </c>
+      <c r="H12" s="52">
+        <v>5.86</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="0"/>
+        <v>94.14</v>
+      </c>
+      <c r="J12" s="6">
+        <f t="shared" si="1"/>
+        <v>2670842.1743999999</v>
+      </c>
+      <c r="K12" s="42">
+        <f t="shared" si="4"/>
+        <v>1.5944602852234029E-2</v>
+      </c>
+      <c r="L12" s="61">
+        <f t="shared" si="2"/>
+        <v>80918.629406315915</v>
+      </c>
+      <c r="M12" s="9">
+        <f t="shared" si="5"/>
+        <v>-1.4434910115454443E-2</v>
+      </c>
+      <c r="N12" s="61">
+        <f t="shared" si="3"/>
+        <v>22561.476122742213</v>
+      </c>
+      <c r="O12" s="42">
+        <f t="shared" si="6"/>
+        <v>3.8314156675365557E-2</v>
+      </c>
+      <c r="Q12">
+        <v>40.729148864746101</v>
+      </c>
+      <c r="R12" s="25">
+        <f t="shared" si="9"/>
+        <v>0.32201004028320313</v>
+      </c>
+      <c r="S12">
+        <v>20.273376429073512</v>
+      </c>
+      <c r="T12">
+        <v>-4.1502986226508227</v>
+      </c>
+      <c r="U12">
+        <v>40109177531.685844</v>
+      </c>
+      <c r="V12">
+        <v>4.0687761270138054E-2</v>
+      </c>
+      <c r="W12">
+        <v>0.13906365808080101</v>
+      </c>
+      <c r="X12">
+        <v>22.593183926345901</v>
+      </c>
+      <c r="Y12" s="25">
+        <f t="shared" si="7"/>
+        <v>-1.1364890411805995</v>
+      </c>
+      <c r="Z12">
+        <v>77.267790000345798</v>
+      </c>
+      <c r="AA12">
+        <v>6.7856716847083803E-3</v>
+      </c>
+      <c r="AB12" s="25">
+        <f t="shared" si="8"/>
+        <v>-1.8600894741257219E-2</v>
+      </c>
+      <c r="AD12">
+        <v>9.9299738486408202</v>
+      </c>
+      <c r="AE12">
+        <v>39.102921622057082</v>
+      </c>
+      <c r="AF12">
+        <v>28.837459653073982</v>
+      </c>
+      <c r="AG12">
+        <v>23.497058193413821</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2010</v>
+      </c>
+      <c r="C13" s="60">
+        <v>247501100140.01782</v>
+      </c>
+      <c r="D13">
+        <v>14.519749710899404</v>
+      </c>
+      <c r="E13" s="60">
+        <v>64325859654.865166</v>
+      </c>
+      <c r="F13">
+        <v>6.7504864541236316</v>
+      </c>
+      <c r="G13">
+        <v>2936802</v>
+      </c>
+      <c r="H13" s="52">
+        <v>4.12</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="0"/>
+        <v>95.88</v>
+      </c>
+      <c r="J13" s="6">
+        <f t="shared" si="1"/>
+        <v>2815805.7576000001</v>
+      </c>
+      <c r="K13" s="42">
+        <f t="shared" si="4"/>
+        <v>5.4276356944440586E-2</v>
+      </c>
+      <c r="L13" s="61">
+        <f t="shared" si="2"/>
+        <v>87897.078650400523</v>
+      </c>
+      <c r="M13" s="9">
+        <f t="shared" si="5"/>
+        <v>8.6240329270084265E-2</v>
+      </c>
+      <c r="N13" s="61">
+        <f t="shared" si="3"/>
+        <v>22844.56570956518</v>
+      </c>
+      <c r="O13" s="42">
+        <f t="shared" si="6"/>
+        <v>1.2547476294674259E-2</v>
+      </c>
+      <c r="Q13">
+        <v>46.475578308105497</v>
+      </c>
+      <c r="R13" s="25">
+        <f t="shared" si="9"/>
+        <v>5.7464294433593963</v>
+      </c>
+      <c r="S13">
+        <v>20.773833025312548</v>
+      </c>
+      <c r="T13">
+        <v>29.675335626760187</v>
+      </c>
+      <c r="U13">
+        <v>52011710581.34671</v>
+      </c>
+      <c r="V13">
+        <v>3.614898888342135E-2</v>
+      </c>
+      <c r="W13">
+        <v>0.13561924621409599</v>
+      </c>
+      <c r="X13">
+        <v>21.723582478803099</v>
+      </c>
+      <c r="Y13" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.86960144754280222</v>
+      </c>
+      <c r="Z13">
+        <v>78.140762763266096</v>
+      </c>
+      <c r="AA13">
+        <v>3.8512160672045999E-2</v>
+      </c>
+      <c r="AB13" s="25">
+        <f t="shared" si="8"/>
+        <v>3.1726488987337619E-2</v>
+      </c>
+      <c r="AD13">
+        <v>9.6915683859659953</v>
+      </c>
+      <c r="AE13">
+        <v>36.337838296581353</v>
+      </c>
+      <c r="AF13">
+        <v>25.569721215450116</v>
+      </c>
+      <c r="AG13">
+        <v>26.312365798407917</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2011</v>
+      </c>
+      <c r="C14" s="60">
+        <v>262883130580.25568</v>
+      </c>
+      <c r="D14">
+        <v>6.2149341685898918</v>
+      </c>
+      <c r="E14" s="60">
+        <v>68420489880.530258</v>
+      </c>
+      <c r="F14">
+        <v>6.3654496770575264</v>
+      </c>
+      <c r="G14">
+        <v>3012462</v>
+      </c>
+      <c r="H14" s="52">
+        <v>3.89</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="0"/>
+        <v>96.11</v>
+      </c>
+      <c r="J14" s="6">
+        <f t="shared" si="1"/>
+        <v>2895277.2281999998</v>
+      </c>
+      <c r="K14" s="42">
+        <f t="shared" si="4"/>
+        <v>2.822334970567561E-2</v>
+      </c>
+      <c r="L14" s="61">
+        <f t="shared" si="2"/>
+        <v>90797.222462765916</v>
+      </c>
+      <c r="M14" s="9">
+        <f t="shared" si="5"/>
+        <v>3.299476907418445E-2</v>
+      </c>
+      <c r="N14" s="61">
+        <f t="shared" si="3"/>
+        <v>23631.757682516443</v>
+      </c>
+      <c r="O14" s="42">
+        <f t="shared" si="6"/>
+        <v>3.4458609673707216E-2</v>
+      </c>
+      <c r="Q14">
+        <v>46.935169219970703</v>
+      </c>
+      <c r="R14" s="25">
+        <f t="shared" si="9"/>
+        <v>0.45959091186520595</v>
+      </c>
+      <c r="S14">
+        <v>19.582551507977822</v>
+      </c>
+      <c r="T14">
+        <v>7.8077670717552081</v>
+      </c>
+      <c r="U14">
+        <v>56072663793.573723</v>
+      </c>
+      <c r="V14">
+        <v>3.4607600751235389E-2</v>
+      </c>
+      <c r="W14">
+        <v>0.13246039834856399</v>
+      </c>
+      <c r="X14">
+        <v>20.7412116291523</v>
+      </c>
+      <c r="Y14" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.98237084965079902</v>
+      </c>
+      <c r="Z14">
+        <v>79.126327972499098</v>
+      </c>
+      <c r="AA14">
+        <v>0.15430144547848201</v>
+      </c>
+      <c r="AB14" s="25">
+        <f t="shared" si="8"/>
+        <v>0.11578928480643602</v>
+      </c>
+      <c r="AD14">
+        <v>9.2368426370194889</v>
+      </c>
+      <c r="AE14">
+        <v>36.615610020152666</v>
+      </c>
+      <c r="AF14">
+        <v>25.264914637905171</v>
+      </c>
+      <c r="AG14">
+        <v>27.556785921536942</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2012</v>
+      </c>
+      <c r="C15" s="60">
+        <v>274543305511.61057</v>
+      </c>
+      <c r="D15">
+        <v>4.4354975937853709</v>
+      </c>
+      <c r="E15" s="60">
+        <v>74324950448.238876</v>
+      </c>
+      <c r="F15">
+        <v>8.6296671918287444</v>
+      </c>
+      <c r="G15">
+        <v>3125729</v>
+      </c>
+      <c r="H15" s="52">
+        <v>3.72</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="0"/>
+        <v>96.28</v>
+      </c>
+      <c r="J15" s="6">
+        <f t="shared" si="1"/>
+        <v>3009451.8812000002</v>
+      </c>
+      <c r="K15" s="42">
+        <f t="shared" si="4"/>
+        <v>3.943479121375297E-2</v>
+      </c>
+      <c r="L15" s="61">
+        <f t="shared" si="2"/>
+        <v>91227.012874563108</v>
+      </c>
+      <c r="M15" s="9">
+        <f t="shared" si="5"/>
+        <v>4.7335193758095443E-3</v>
+      </c>
+      <c r="N15" s="61">
+        <f t="shared" si="3"/>
+        <v>24697.171904473937</v>
+      </c>
+      <c r="O15" s="42">
+        <f t="shared" si="6"/>
+        <v>4.5084002479668366E-2</v>
+      </c>
+      <c r="Q15">
+        <v>48.682609558105497</v>
+      </c>
+      <c r="R15" s="25">
+        <f t="shared" si="9"/>
+        <v>1.747440338134794</v>
+      </c>
+      <c r="S15">
+        <v>19.116821980066192</v>
+      </c>
+      <c r="T15">
+        <v>0.31910712270446595</v>
+      </c>
+      <c r="U15">
+        <v>56251595657.629143</v>
+      </c>
+      <c r="V15">
+        <v>3.3272726533169004E-2</v>
+      </c>
+      <c r="W15">
+        <v>0.12955873329242601</v>
+      </c>
+      <c r="X15">
+        <v>20.3739028359523</v>
+      </c>
+      <c r="Y15" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.36730879319999943</v>
+      </c>
+      <c r="Z15">
+        <v>79.496505082303997</v>
+      </c>
+      <c r="AA15">
+        <v>0.14329419862700701</v>
+      </c>
+      <c r="AB15" s="25">
+        <f t="shared" si="8"/>
+        <v>-1.1007246851475E-2</v>
+      </c>
+      <c r="AD15">
+        <v>8.8578668846884447</v>
+      </c>
+      <c r="AE15">
+        <v>37.306048070547945</v>
+      </c>
+      <c r="AF15">
+        <v>26.429988298955582</v>
+      </c>
+      <c r="AG15">
+        <v>24.226259963852854</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2013</v>
+      </c>
+      <c r="C16" s="60">
+        <v>287769788882.22137</v>
+      </c>
+      <c r="D16">
+        <v>4.8176309912067552</v>
+      </c>
+      <c r="E16" s="60">
+        <v>78902551233.793396</v>
+      </c>
+      <c r="F16">
+        <v>6.1589019003012169</v>
+      </c>
+      <c r="G16">
+        <v>3179345</v>
+      </c>
+      <c r="H16" s="52">
+        <v>3.86</v>
+      </c>
+      <c r="I16" s="6">
+        <f t="shared" si="0"/>
+        <v>96.14</v>
+      </c>
+      <c r="J16" s="6">
+        <f t="shared" si="1"/>
+        <v>3056622.2830000003</v>
+      </c>
+      <c r="K16" s="42">
+        <f t="shared" si="4"/>
+        <v>1.5674084073140655E-2</v>
+      </c>
+      <c r="L16" s="61">
+        <f t="shared" si="2"/>
+        <v>94146.336131457603</v>
+      </c>
+      <c r="M16" s="9">
+        <f t="shared" si="5"/>
+        <v>3.2000645038203282E-2</v>
+      </c>
+      <c r="N16" s="61">
+        <f t="shared" si="3"/>
+        <v>25813.641310090974</v>
+      </c>
+      <c r="O16" s="42">
+        <f t="shared" si="6"/>
+        <v>4.5206366540080929E-2</v>
+      </c>
+      <c r="Q16">
+        <v>50.001869201660199</v>
+      </c>
+      <c r="R16" s="25">
+        <f t="shared" si="9"/>
+        <v>1.3192596435547017</v>
+      </c>
+      <c r="S16">
+        <v>17.638409614875453</v>
+      </c>
+      <c r="T16">
+        <v>1.6712764155420388</v>
+      </c>
+      <c r="U16">
+        <v>57191715309.221169</v>
+      </c>
+      <c r="V16">
+        <v>3.4375216793813404E-2</v>
+      </c>
+      <c r="W16">
+        <v>0.12679854020966699</v>
+      </c>
+      <c r="X16">
+        <v>19.685489766741199</v>
+      </c>
+      <c r="Y16" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.68841306921110146</v>
+      </c>
+      <c r="Z16">
+        <v>80.187678894668295</v>
+      </c>
+      <c r="AA16">
+        <v>0.119459449682427</v>
+      </c>
+      <c r="AB16" s="25">
+        <f t="shared" si="8"/>
+        <v>-2.3834748944580014E-2</v>
+      </c>
+      <c r="AD16">
+        <v>9.7442177273746502</v>
+      </c>
+      <c r="AE16">
+        <v>37.333460129295503</v>
+      </c>
+      <c r="AF16">
+        <v>27.548215593668829</v>
+      </c>
+      <c r="AG16">
+        <v>23.113812627266899</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2014</v>
+      </c>
+      <c r="C17" s="60">
+        <v>299095084828.97827</v>
+      </c>
+      <c r="D17">
+        <v>3.9355402770900696</v>
+      </c>
+      <c r="E17" s="60">
+        <v>82232429581.946793</v>
+      </c>
+      <c r="F17">
+        <v>4.2202416729045353</v>
+      </c>
+      <c r="G17">
+        <v>3266959</v>
+      </c>
+      <c r="H17" s="52">
+        <v>3.74</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="0"/>
+        <v>96.26</v>
+      </c>
+      <c r="J17" s="6">
+        <f t="shared" si="1"/>
+        <v>3144774.7334000003</v>
+      </c>
+      <c r="K17" s="42">
+        <f t="shared" si="4"/>
+        <v>2.8839824563956423E-2</v>
+      </c>
+      <c r="L17" s="61">
+        <f t="shared" si="2"/>
+        <v>95108.588113594087</v>
+      </c>
+      <c r="M17" s="9">
+        <f t="shared" si="5"/>
+        <v>1.0220811788075115E-2</v>
+      </c>
+      <c r="N17" s="61">
+        <f t="shared" si="3"/>
+        <v>26148.909398365871</v>
+      </c>
+      <c r="O17" s="42">
+        <f t="shared" si="6"/>
+        <v>1.298801994834551E-2</v>
+      </c>
+      <c r="Q17">
+        <v>51.152580261230497</v>
+      </c>
+      <c r="R17" s="25">
+        <f t="shared" si="9"/>
+        <v>1.1507110595702983</v>
+      </c>
+      <c r="S17">
+        <v>17.999768892128522</v>
+      </c>
+      <c r="T17">
+        <v>2.6831203913080088</v>
+      </c>
+      <c r="U17">
+        <v>58726237884.821701</v>
+      </c>
+      <c r="V17">
+        <v>3.4540851073536168E-2</v>
+      </c>
+      <c r="W17">
+        <v>0.124092213197688</v>
+      </c>
+      <c r="X17">
+        <v>17.5887805852729</v>
+      </c>
+      <c r="Y17" s="25">
+        <f t="shared" si="7"/>
+        <v>-2.0967091814682988</v>
+      </c>
+      <c r="Z17">
+        <v>82.287159069072601</v>
+      </c>
+      <c r="AA17">
+        <v>0.10487946932588101</v>
+      </c>
+      <c r="AB17" s="25">
+        <f t="shared" si="8"/>
+        <v>-1.4579980356545993E-2</v>
+      </c>
+      <c r="AD17">
+        <v>9.6310320219758019</v>
+      </c>
+      <c r="AE17">
+        <v>37.584381318964205</v>
+      </c>
+      <c r="AF17">
+        <v>28.128209222306971</v>
+      </c>
+      <c r="AG17">
+        <v>23.439752408773177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2015</v>
+      </c>
+      <c r="C18" s="60">
+        <v>307998545269.39795</v>
+      </c>
+      <c r="D18">
+        <v>2.9767993163480639</v>
+      </c>
+      <c r="E18" s="60">
+        <v>83844198352.517593</v>
+      </c>
+      <c r="F18">
+        <v>1.9600159921878912</v>
+      </c>
+      <c r="G18">
+        <v>3360400</v>
+      </c>
+      <c r="H18" s="52">
+        <v>3.79</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="0"/>
+        <v>96.21</v>
+      </c>
+      <c r="J18" s="6">
+        <f t="shared" si="1"/>
+        <v>3233040.84</v>
+      </c>
+      <c r="K18" s="42">
+        <f t="shared" si="4"/>
+        <v>2.8067545081224287E-2</v>
+      </c>
+      <c r="L18" s="61">
+        <f t="shared" si="2"/>
+        <v>95265.899972175408</v>
+      </c>
+      <c r="M18" s="9">
+        <f t="shared" si="5"/>
+        <v>1.6540236975596098E-3</v>
+      </c>
+      <c r="N18" s="61">
+        <f t="shared" si="3"/>
+        <v>25933.541363033819</v>
+      </c>
+      <c r="O18" s="42">
+        <f t="shared" si="6"/>
+        <v>-8.2362148283519395E-3</v>
+      </c>
+      <c r="Q18">
+        <v>52.041000366210902</v>
+      </c>
+      <c r="R18" s="25">
+        <f t="shared" si="9"/>
+        <v>0.8884201049804048</v>
+      </c>
+      <c r="S18">
+        <v>18.089329854873405</v>
+      </c>
+      <c r="T18">
+        <v>-5.1278017991461269</v>
+      </c>
+      <c r="U18">
+        <v>55714872801.992981</v>
+      </c>
+      <c r="V18">
+        <v>3.2613513802648333E-2</v>
+      </c>
+      <c r="W18">
+        <v>0.12145966005548101</v>
+      </c>
+      <c r="X18">
+        <v>17.2904642702552</v>
+      </c>
+      <c r="Y18" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.29831631501770062</v>
+      </c>
+      <c r="Z18">
+        <v>82.588076069689293</v>
+      </c>
+      <c r="AA18">
+        <v>3.4391157293545603E-2</v>
+      </c>
+      <c r="AB18" s="25">
+        <f t="shared" si="8"/>
+        <v>-7.048831203233541E-2</v>
+      </c>
+      <c r="AD18">
+        <v>10.19090831587924</v>
+      </c>
+      <c r="AE18">
+        <v>37.158080606153213</v>
+      </c>
+      <c r="AF18">
+        <v>27.222270897150295</v>
+      </c>
+      <c r="AG18">
+        <v>27.297818059101541</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2016</v>
+      </c>
+      <c r="C19" s="60">
+        <v>319541032495.04486</v>
+      </c>
+      <c r="D19">
+        <v>3.7475784879279246</v>
+      </c>
+      <c r="E19" s="60">
+        <v>84290655174.294907</v>
+      </c>
+      <c r="F19">
+        <v>0.53248385761912687</v>
+      </c>
+      <c r="G19">
+        <v>3396546</v>
+      </c>
+      <c r="H19" s="52">
+        <v>4.08</v>
+      </c>
+      <c r="I19" s="6">
+        <f t="shared" si="0"/>
+        <v>95.92</v>
+      </c>
+      <c r="J19" s="6">
+        <f t="shared" si="1"/>
+        <v>3257966.9232000001</v>
+      </c>
+      <c r="K19" s="42">
+        <f t="shared" si="4"/>
+        <v>7.7097953393005167E-3</v>
+      </c>
+      <c r="L19" s="61">
+        <f t="shared" si="2"/>
+        <v>98079.888478790701</v>
+      </c>
+      <c r="M19" s="9">
+        <f t="shared" si="5"/>
+        <v>2.9538255634357968E-2</v>
+      </c>
+      <c r="N19" s="61">
+        <f t="shared" si="3"/>
+        <v>25872.164193583641</v>
+      </c>
+      <c r="O19" s="42">
+        <f t="shared" si="6"/>
+        <v>-2.3667099140445851E-3</v>
+      </c>
+      <c r="Q19">
+        <v>52.7865180969238</v>
+      </c>
+      <c r="R19" s="25">
+        <f t="shared" si="9"/>
+        <v>0.74551773071289773</v>
+      </c>
+      <c r="S19">
+        <v>17.441961312599027</v>
+      </c>
+      <c r="T19">
+        <v>3.7010008068074569</v>
+      </c>
+      <c r="U19">
+        <v>57776880693.906494</v>
+      </c>
+      <c r="V19">
+        <v>3.1521289438126224E-2</v>
+      </c>
+      <c r="W19">
+        <v>0.11897925916280699</v>
+      </c>
+      <c r="X19">
+        <v>16.156803308709499</v>
+      </c>
+      <c r="Y19" s="25">
+        <f t="shared" si="7"/>
+        <v>-1.1336609615457007</v>
+      </c>
+      <c r="Z19">
+        <v>83.724217432127702</v>
+      </c>
+      <c r="AA19">
+        <v>2.9353972319112E-2</v>
+      </c>
+      <c r="AB19" s="25">
+        <f t="shared" si="8"/>
+        <v>-5.0371849744336034E-3</v>
+      </c>
+      <c r="AD19">
+        <v>10.200372971650724</v>
+      </c>
+      <c r="AE19">
+        <v>36.336754045415525</v>
+      </c>
+      <c r="AF19">
+        <v>25.877029477577924</v>
+      </c>
+      <c r="AG19">
+        <v>26.253769658413212</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2017</v>
+      </c>
+      <c r="C20" s="60">
+        <v>333846562289.74597</v>
+      </c>
+      <c r="D20">
+        <v>4.4768991584587638</v>
+      </c>
+      <c r="E20" s="60">
+        <v>88598330696.634109</v>
+      </c>
+      <c r="F20">
+        <v>5.1105018859230142</v>
+      </c>
+      <c r="G20">
+        <v>3388507</v>
+      </c>
+      <c r="H20" s="52">
+        <v>4.2</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="0"/>
+        <v>95.8</v>
+      </c>
+      <c r="J20" s="6">
+        <f t="shared" si="1"/>
+        <v>3246189.7059999998</v>
+      </c>
+      <c r="K20" s="42">
+        <f t="shared" si="4"/>
+        <v>-3.6148977192293381E-3</v>
+      </c>
+      <c r="L20" s="61">
+        <f t="shared" si="2"/>
+        <v>102842.59163064021</v>
+      </c>
+      <c r="M20" s="9">
+        <f t="shared" si="5"/>
+        <v>4.8559426664513565E-2</v>
+      </c>
+      <c r="N20" s="61">
+        <f t="shared" si="3"/>
+        <v>27293.023119651934</v>
+      </c>
+      <c r="O20" s="42">
+        <f t="shared" si="6"/>
+        <v>5.4918441126029546E-2</v>
+      </c>
+      <c r="Q20">
+        <v>54.232109069824197</v>
+      </c>
+      <c r="R20" s="25">
+        <f t="shared" si="9"/>
+        <v>1.4455909729003977</v>
+      </c>
+      <c r="S20">
+        <v>18.545847537786003</v>
+      </c>
+      <c r="T20">
+        <v>10.406115334791167</v>
+      </c>
+      <c r="U20">
+        <v>63789209535.759094</v>
+      </c>
+      <c r="V20">
+        <v>3.0763583755226389E-2</v>
+      </c>
+      <c r="W20">
+        <v>0.117077595142899</v>
+      </c>
+      <c r="X20">
+        <v>15.8830026161212</v>
+      </c>
+      <c r="Y20" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.2738006925882992</v>
+      </c>
+      <c r="Z20">
+        <v>83.999919788735895</v>
+      </c>
+      <c r="AA20">
+        <v>4.52888881904618E-4</v>
+      </c>
+      <c r="AB20" s="25">
+        <f t="shared" si="8"/>
+        <v>-2.8901083437207382E-2</v>
+      </c>
+      <c r="AD20">
+        <v>10.140018759338188</v>
+      </c>
+      <c r="AE20">
+        <v>35.184722354653985</v>
+      </c>
+      <c r="AF20">
+        <v>25.115649681750725</v>
+      </c>
+      <c r="AG20">
+        <v>26.545597667222111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="3">
+        <v>2018</v>
+      </c>
+      <c r="C21" s="60">
+        <v>345370865382.86688</v>
+      </c>
+      <c r="D21">
+        <v>3.4519759658686979</v>
+      </c>
+      <c r="E21" s="60">
+        <v>84207444583.856125</v>
+      </c>
+      <c r="F21">
+        <v>-4.9559467749032819</v>
+      </c>
+      <c r="G21">
+        <v>3390276</v>
+      </c>
+      <c r="H21" s="52">
+        <v>3.613</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="shared" si="0"/>
+        <v>96.387</v>
+      </c>
+      <c r="J21" s="6">
+        <f t="shared" si="1"/>
+        <v>3267785.3281200002</v>
+      </c>
+      <c r="K21" s="42">
+        <f t="shared" si="4"/>
+        <v>6.652606309509511E-3</v>
+      </c>
+      <c r="L21" s="61">
+        <f t="shared" si="2"/>
+        <v>105689.58199636794</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" si="5"/>
+        <v>2.7682989319762721E-2</v>
+      </c>
+      <c r="N21" s="61">
+        <f t="shared" si="3"/>
+        <v>25768.964643801057</v>
+      </c>
+      <c r="O21" s="42">
+        <f t="shared" si="6"/>
+        <v>-5.5840588606452392E-2</v>
+      </c>
+      <c r="Q21">
+        <v>55.760608673095703</v>
+      </c>
+      <c r="R21" s="25">
+        <f t="shared" si="9"/>
+        <v>1.5284996032715057</v>
+      </c>
+      <c r="S21">
+        <v>20.717845766781217</v>
+      </c>
+      <c r="T21">
+        <v>7.0287004412821261</v>
+      </c>
+      <c r="U21">
+        <v>68272761987.889374</v>
+      </c>
+      <c r="V21">
+        <v>3.0117148236328394E-2</v>
+      </c>
+      <c r="W21">
+        <v>0.115089283007242</v>
+      </c>
+      <c r="X21">
+        <v>16.038846154906299</v>
+      </c>
+      <c r="Y21" s="25">
+        <f t="shared" si="7"/>
+        <v>0.15584353878509916</v>
+      </c>
+      <c r="Z21">
+        <v>83.846064562086497</v>
+      </c>
+      <c r="AA21">
+        <v>1.8876715293803699E-4</v>
+      </c>
+      <c r="AB21" s="25">
+        <f t="shared" si="8"/>
+        <v>-2.6412172896658097E-4</v>
+      </c>
+      <c r="AD21">
+        <v>9.9398348941138064</v>
+      </c>
+      <c r="AE21">
+        <v>34.614491407338598</v>
+      </c>
+      <c r="AF21">
+        <v>22.351805620065026</v>
+      </c>
+      <c r="AG21">
+        <v>29.700268952184881</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C22" s="60">
+        <v>349888458531.08569</v>
+      </c>
+      <c r="D22">
+        <v>1.3080411815312658</v>
+      </c>
+      <c r="E22" s="60">
+        <v>86300365501.063766</v>
+      </c>
+      <c r="F22">
+        <v>2.4854345450697792</v>
+      </c>
+      <c r="G22">
+        <v>3454121</v>
+      </c>
+      <c r="H22" s="52">
+        <v>3.1</v>
+      </c>
+      <c r="I22" s="6">
+        <f t="shared" si="0"/>
+        <v>96.9</v>
+      </c>
+      <c r="J22" s="6">
+        <f t="shared" si="1"/>
+        <v>3347043.2490000003</v>
+      </c>
+      <c r="K22" s="42">
+        <f t="shared" si="4"/>
+        <v>2.4254323011358346E-2</v>
+      </c>
+      <c r="L22" s="61">
+        <f t="shared" si="2"/>
+        <v>104536.58124543872</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" si="5"/>
+        <v>-1.0909313190100821E-2</v>
+      </c>
+      <c r="N22" s="61">
+        <f t="shared" si="3"/>
+        <v>25784.060461975751</v>
+      </c>
+      <c r="O22" s="42">
+        <f t="shared" si="6"/>
+        <v>5.8581391931573521E-4</v>
+      </c>
+      <c r="Q22">
+        <v>57.249900817871101</v>
+      </c>
+      <c r="R22" s="25">
+        <f t="shared" si="9"/>
+        <v>1.4892921447753977</v>
+      </c>
+      <c r="S22">
+        <v>19.40403130191034</v>
+      </c>
+      <c r="T22">
+        <v>-1.4550979032228923</v>
+      </c>
+      <c r="U22">
+        <v>67279326459.731239</v>
+      </c>
+      <c r="V22">
+        <v>3.2252130199608528E-2</v>
+      </c>
+      <c r="W22">
+        <v>0.113041897035994</v>
+      </c>
+      <c r="X22">
+        <v>14.9655328914049</v>
+      </c>
+      <c r="Y22" s="25">
+        <f t="shared" si="7"/>
+        <v>-1.0733132635013991</v>
+      </c>
+      <c r="Z22">
+        <v>84.921455267899702</v>
+      </c>
+      <c r="AA22">
+        <v>1.6926616042902101E-4</v>
+      </c>
+      <c r="AB22" s="25">
+        <f t="shared" si="8"/>
+        <v>-1.9500992509015986E-5</v>
+      </c>
+      <c r="AD22">
+        <v>10.253396494246401</v>
+      </c>
+      <c r="AE22">
+        <v>35.845393881281687</v>
+      </c>
+      <c r="AF22">
+        <v>22.799478885505962</v>
+      </c>
+      <c r="AG22">
+        <v>29.367995967723893</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C23" s="60">
+        <v>336541232520.5025</v>
+      </c>
+      <c r="D23">
+        <v>-3.8147088551071278</v>
+      </c>
+      <c r="E23" s="60">
+        <v>74186532831.451279</v>
+      </c>
+      <c r="F23">
+        <v>-14.036826610500484</v>
+      </c>
+      <c r="G23">
+        <v>3431193</v>
+      </c>
+      <c r="H23" s="52">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="0"/>
+        <v>95.9</v>
+      </c>
+      <c r="J23" s="6">
+        <f t="shared" si="1"/>
+        <v>3290514.0870000003</v>
+      </c>
+      <c r="K23" s="42">
+        <f t="shared" si="4"/>
+        <v>-1.6889283404655522E-2</v>
+      </c>
+      <c r="L23" s="61">
+        <f t="shared" si="2"/>
+        <v>102276.18652358696</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="5"/>
+        <v>-2.1623002157920537E-2</v>
+      </c>
+      <c r="N23" s="61">
+        <f t="shared" si="3"/>
+        <v>22545.575211041869</v>
+      </c>
+      <c r="O23" s="42">
+        <f t="shared" si="6"/>
+        <v>-0.12560028144945354</v>
+      </c>
+      <c r="Q23">
+        <v>58.2861518859863</v>
+      </c>
+      <c r="R23" s="25">
+        <f t="shared" si="9"/>
+        <v>1.0362510681151988</v>
+      </c>
+      <c r="S23">
+        <v>19.653984525036179</v>
+      </c>
+      <c r="T23">
+        <v>7.5307063016974496</v>
+      </c>
+      <c r="U23">
+        <v>72345934937.173828</v>
+      </c>
+      <c r="V23">
+        <v>3.281725211869508E-2</v>
+      </c>
+      <c r="W23">
+        <v>0.108162685533748</v>
+      </c>
+      <c r="X23">
+        <v>14.8295407728436</v>
+      </c>
+      <c r="Y23" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.13599211856129934</v>
+      </c>
+      <c r="Z23">
+        <v>85.0622965416227</v>
+      </c>
+      <c r="AA23">
+        <v>2.4207226855628999E-4</v>
+      </c>
+      <c r="AB23" s="25">
+        <f t="shared" si="8"/>
+        <v>7.2806108127268987E-5</v>
+      </c>
+      <c r="AD23">
+        <v>12.190147791383446</v>
+      </c>
+      <c r="AE23">
+        <v>32.147432325908682</v>
+      </c>
+      <c r="AF23">
+        <v>20.999459350147131</v>
+      </c>
+      <c r="AG23">
+        <v>31.279400415186071</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2021</v>
+      </c>
+      <c r="C24" s="60">
+        <v>369376902514.86536</v>
+      </c>
+      <c r="D24">
+        <v>9.7568044629903028</v>
+      </c>
+      <c r="E24" s="60">
+        <v>91394322913.825394</v>
+      </c>
+      <c r="F24">
+        <v>23.19530166138037</v>
+      </c>
+      <c r="G24">
+        <v>3385810</v>
+      </c>
+      <c r="H24" s="52">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="0"/>
+        <v>95.36</v>
+      </c>
+      <c r="J24" s="6">
+        <f t="shared" si="1"/>
+        <v>3228708.4160000002</v>
+      </c>
+      <c r="K24" s="42">
+        <f t="shared" si="4"/>
+        <v>-1.878298325607505E-2</v>
+      </c>
+      <c r="L24" s="61">
+        <f t="shared" si="2"/>
+        <v>114403.92098722901</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="5"/>
+        <v>0.11857828176694038</v>
+      </c>
+      <c r="N24" s="61">
+        <f t="shared" si="3"/>
+        <v>28306.775074799876</v>
+      </c>
+      <c r="O24" s="42">
+        <f t="shared" si="6"/>
+        <v>0.25553572307777783</v>
+      </c>
+      <c r="Q24">
+        <v>61.837471008300803</v>
+      </c>
+      <c r="R24" s="25">
+        <f t="shared" si="9"/>
+        <v>3.5513191223145029</v>
+      </c>
+      <c r="S24">
+        <v>20.633068003561824</v>
+      </c>
+      <c r="T24">
+        <v>13.303540009852924</v>
+      </c>
+      <c r="U24">
+        <v>81970505337.042892</v>
+      </c>
+      <c r="V24">
+        <v>3.0551368665513827E-2</v>
+      </c>
+      <c r="W24">
+        <v>0.107777556138585</v>
+      </c>
+      <c r="X24">
+        <v>14.4449638584304</v>
+      </c>
+      <c r="Y24" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.3845769144132003</v>
+      </c>
+      <c r="Z24">
+        <v>85.447258585431001</v>
+      </c>
+      <c r="AA24">
+        <v>1.80989109199595E-4</v>
+      </c>
+      <c r="AB24" s="25">
+        <f t="shared" si="8"/>
+        <v>-6.1083159356694992E-5</v>
+      </c>
+      <c r="AD24">
+        <v>10.532697743092175</v>
+      </c>
+      <c r="AE24">
+        <v>28.780240455600087</v>
+      </c>
+      <c r="AF24">
+        <v>22.078228221894115</v>
+      </c>
+      <c r="AG24">
+        <v>35.785344863952751</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C25" s="60">
+        <v>384550906479.00623</v>
+      </c>
+      <c r="D25">
+        <v>4.1080002189715117</v>
+      </c>
+      <c r="E25" s="60">
+        <v>95674867710.435883</v>
+      </c>
+      <c r="F25">
+        <v>4.6836003157948483</v>
+      </c>
+      <c r="G25">
+        <v>3459003</v>
+      </c>
+      <c r="H25" s="52">
+        <v>3.5910000000000002</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="0"/>
+        <v>96.409000000000006</v>
+      </c>
+      <c r="J25" s="6">
+        <f t="shared" si="1"/>
+        <v>3334790.2022700002</v>
+      </c>
+      <c r="K25" s="42">
+        <f t="shared" si="4"/>
+        <v>3.285579637489322E-2</v>
+      </c>
+      <c r="L25" s="61">
+        <f t="shared" si="2"/>
+        <v>115314.87234706442</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="5"/>
+        <v>7.9625886243627955E-3</v>
+      </c>
+      <c r="N25" s="61">
+        <f t="shared" si="3"/>
+        <v>28689.921076687151</v>
+      </c>
+      <c r="O25" s="42">
+        <f t="shared" si="6"/>
+        <v>1.3535487559950652E-2</v>
+      </c>
+      <c r="Q25">
+        <v>63.086940765380902</v>
+      </c>
+      <c r="R25" s="25">
+        <f t="shared" si="9"/>
+        <v>1.2494697570800994</v>
+      </c>
+      <c r="S25">
+        <v>19.655537649937781</v>
+      </c>
+      <c r="T25">
+        <v>2.6997624563978491</v>
+      </c>
+      <c r="U25">
+        <v>84183514265.451965</v>
+      </c>
+      <c r="V25">
+        <v>2.597731637364643E-2</v>
+      </c>
+      <c r="W25">
+        <v>9.0952445633474793E-2</v>
+      </c>
+      <c r="X25">
+        <v>14.5645681583865</v>
+      </c>
+      <c r="Y25" s="25">
+        <f t="shared" si="7"/>
+        <v>0.11960429995609978</v>
+      </c>
+      <c r="Z25">
+        <v>85.344449477412397</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB25" s="46" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD25">
+        <v>9.1289494952629333</v>
+      </c>
+      <c r="AE25">
+        <v>28.099108159151914</v>
+      </c>
+      <c r="AF25">
+        <v>20.338964403941983</v>
+      </c>
+      <c r="AG25">
+        <v>39.774395154749833</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C26" s="60">
+        <v>391555143381.88489</v>
+      </c>
+      <c r="D26">
+        <v>1.8214069411538532</v>
+      </c>
+      <c r="E26" s="60">
+        <v>94809012056.079865</v>
+      </c>
+      <c r="F26">
+        <v>-0.90499801575536765</v>
+      </c>
+      <c r="G26">
+        <v>3622441</v>
+      </c>
+      <c r="H26" s="52">
+        <v>3.444</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="0"/>
+        <v>96.555999999999997</v>
+      </c>
+      <c r="J26" s="6">
+        <f t="shared" si="1"/>
+        <v>3497684.1319599999</v>
+      </c>
+      <c r="K26" s="42">
+        <f t="shared" si="4"/>
+        <v>4.8846829878268612E-2</v>
+      </c>
+      <c r="L26" s="61">
+        <f t="shared" si="2"/>
+        <v>111946.97079820893</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="5"/>
+        <v>-2.9206133435408722E-2</v>
+      </c>
+      <c r="N26" s="61">
+        <f t="shared" si="3"/>
+        <v>27106.224713022231</v>
+      </c>
+      <c r="O26" s="42">
+        <f t="shared" si="6"/>
+        <v>-5.5200443369354521E-2</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>169</v>
+      </c>
+      <c r="R26" s="46"/>
+      <c r="S26">
+        <v>16.975559443779353</v>
+      </c>
+      <c r="T26">
+        <v>-4.2302587923025925</v>
+      </c>
+      <c r="U26">
+        <v>80622333751.568375</v>
+      </c>
+      <c r="V26">
+        <v>2.8849802007551339E-2</v>
+      </c>
+      <c r="W26">
+        <v>7.9580186024164501E-2</v>
+      </c>
+      <c r="X26">
+        <v>13.8432992197459</v>
+      </c>
+      <c r="Y26" s="25">
+        <f t="shared" si="7"/>
+        <v>-0.72126893864060015</v>
+      </c>
+      <c r="Z26">
+        <v>86.077120594229896</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB26" s="46" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD26">
+        <v>9.8421032695316715</v>
+      </c>
+      <c r="AE26">
+        <v>31.513116296958909</v>
+      </c>
+      <c r="AF26">
+        <v>21.87302410554809</v>
+      </c>
+      <c r="AG26">
+        <v>37.158805824026295</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C27" s="60">
+        <v>408736675576.89142</v>
+      </c>
+      <c r="D27">
+        <v>4.3880236246186541</v>
+      </c>
+      <c r="E27" s="60">
+        <v>97592930009.273911</v>
+      </c>
+      <c r="F27">
+        <v>2.9363431733128351</v>
+      </c>
+      <c r="G27">
+        <v>3689424</v>
+      </c>
+      <c r="H27" s="52">
+        <v>2.7370000000000001</v>
+      </c>
+      <c r="I27" s="6">
+        <f t="shared" si="0"/>
+        <v>97.263000000000005</v>
+      </c>
+      <c r="J27" s="6">
+        <f t="shared" si="1"/>
+        <v>3588444.4651200003</v>
+      </c>
+      <c r="K27" s="42">
+        <f t="shared" si="4"/>
+        <v>2.5948693402780471E-2</v>
+      </c>
+      <c r="L27" s="61">
+        <f t="shared" si="2"/>
+        <v>113903.58121739051</v>
+      </c>
+      <c r="M27" s="9">
+        <f t="shared" si="5"/>
+        <v>1.7478011287223569E-2</v>
+      </c>
+      <c r="N27" s="61">
+        <f t="shared" si="3"/>
+        <v>27196.444297211754</v>
+      </c>
+      <c r="O27" s="42">
+        <f t="shared" si="6"/>
+        <v>3.3283714403127447E-3</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>169</v>
+      </c>
+      <c r="R27" s="46"/>
+      <c r="S27">
+        <v>16.332704934853503</v>
+      </c>
+      <c r="T27">
+        <v>4.2628399445695493</v>
+      </c>
+      <c r="U27">
+        <v>84059134798.974411</v>
+      </c>
+      <c r="V27">
+        <v>2.7439170694473516E-2</v>
+      </c>
+      <c r="W27">
+        <v>9.7983733027354095E-2</v>
+      </c>
+      <c r="X27">
+        <v>14.162557810979401</v>
+      </c>
+      <c r="Y27" s="25">
+        <f t="shared" si="7"/>
+        <v>0.31925859123350087</v>
+      </c>
+      <c r="Z27">
+        <v>85.739458455993301</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB27" s="46" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD27">
+        <v>10.05318763287927</v>
+      </c>
+      <c r="AE27">
+        <v>30.684280484260235</v>
+      </c>
+      <c r="AF27">
+        <v>21.037456033494557</v>
+      </c>
+      <c r="AG27">
+        <v>36.012331849548822</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0722AECA-F9D8-4E94-9029-29AE891E1F4A}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.06640625" style="6"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -10991,7 +12007,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>140533304238.72125</v>
       </c>
@@ -11002,7 +12018,7 @@
         <v>2058990.2999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>139028385430.87299</v>
       </c>
@@ -11017,7 +12033,7 @@
       </c>
       <c r="F3" s="14"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>144482970559.8894</v>
       </c>
@@ -11034,7 +12050,7 @@
         <v>0.98087740551070124</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>151054425108.65015</v>
       </c>
@@ -11051,7 +12067,7 @@
         <v>0.96212048464140454</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>166069208808.39377</v>
       </c>
@@ -11068,7 +12084,7 @@
         <v>0.95867689233607767</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>178302402123.90665</v>
       </c>
@@ -11085,7 +12101,7 @@
         <v>17652168151.839451</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>194361682395.94128</v>
       </c>
@@ -11102,7 +12118,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>211896059498.4816</v>
       </c>
@@ -11113,7 +12129,7 @@
         <v>2431366.5179999997</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>215844707508.2283</v>
       </c>
@@ -11127,7 +12143,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>216120888113.03256</v>
       </c>
@@ -11154,7 +12170,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>247501100140.01782</v>
       </c>
@@ -11183,7 +12199,7 @@
         <v>2.3038200450523506E-16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>262883130580.25568</v>
       </c>
@@ -11206,7 +12222,7 @@
         <v>3.1159904046081507E+20</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>274543305511.61057</v>
       </c>
@@ -11229,7 +12245,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>287769788882.22137</v>
       </c>
@@ -11240,7 +12256,7 @@
         <v>3056622.2830000003</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>299095084828.97827</v>
       </c>
@@ -11276,7 +12292,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>307998545269.39795</v>
       </c>
@@ -11314,7 +12330,7 @@
         <v>-19897117643.188736</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>319541032495.04486</v>
       </c>
@@ -11352,7 +12368,7 @@
         <v>3.6960153322484635</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>333846562289.74597</v>
       </c>
@@ -11390,7 +12406,7 @@
         <v>167381.23715056467</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>345370865382.86688</v>
       </c>
@@ -11401,7 +12417,7 @@
         <v>3267785.3281200002</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>349888458531.08569</v>
       </c>
@@ -11412,7 +12428,7 @@
         <v>3347043.2490000003</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>336541232520.5025</v>
       </c>
@@ -11423,7 +12439,7 @@
         <v>3290514.0870000003</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>369376902514.86536</v>
       </c>
@@ -11434,7 +12450,7 @@
         <v>3228708.4160000002</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>384550906479.00623</v>
       </c>
@@ -11445,7 +12461,7 @@
         <v>3334790.2022700002</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>391555143381.88489</v>
       </c>
@@ -11456,7 +12472,7 @@
         <v>3497684.1319599999</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>408736675576.89142</v>
       </c>
@@ -11467,7 +12483,7 @@
         <v>3588444.4651200003</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C28" s="1"/>
     </row>
   </sheetData>
@@ -11479,16 +12495,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E65112-9F7A-4E65-AF87-66BF12EAFA09}">
   <dimension ref="A1:Q33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="9.06640625" style="43"/>
-    <col min="6" max="6" width="13.33203125" style="25" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="42"/>
+    <col min="6" max="6" width="13.28515625" style="25" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" ht="120" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
@@ -11501,7 +12517,7 @@
       <c r="D1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F1" s="40" t="s">
@@ -11514,7 +12530,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -11528,7 +12544,7 @@
         <v>11.414764762166143</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -11541,7 +12557,7 @@
       <c r="D3">
         <v>-5.2071925730891024</v>
       </c>
-      <c r="E3" s="43">
+      <c r="E3" s="42">
         <v>3.1078337377305879E-2</v>
       </c>
       <c r="G3" s="25">
@@ -11552,7 +12568,7 @@
       </c>
       <c r="J3" s="14"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -11565,7 +12581,7 @@
       <c r="D4">
         <v>-9.1539886402542265</v>
       </c>
-      <c r="E4" s="43">
+      <c r="E4" s="42">
         <v>-2.1927623777409942E-2</v>
       </c>
       <c r="G4" s="25">
@@ -11578,7 +12594,7 @@
         <v>0.82393292350564329</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -11591,7 +12607,7 @@
       <c r="D5">
         <v>-5.1563726039681654</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="42">
         <v>-1.4019524271750093E-2</v>
       </c>
       <c r="G5" s="25">
@@ -11604,7 +12620,7 @@
         <v>0.67886546243655621</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>75</v>
       </c>
@@ -11617,7 +12633,7 @@
       <c r="D6">
         <v>10.294087680187801</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="42">
         <v>1.6981685674058087E-2</v>
       </c>
       <c r="G6" s="25">
@@ -11630,7 +12646,7 @@
         <v>0.55041164741117865</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -11643,7 +12659,7 @@
       <c r="D7">
         <v>3.6398739965450631</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="42">
         <v>4.3720826643852136E-2</v>
       </c>
       <c r="G7" s="25">
@@ -11656,26 +12672,26 @@
         <v>2.8961175812830007</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="44" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="44" t="s">
+    <row r="8" spans="1:17" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="44">
+      <c r="B8" s="43">
         <v>2006</v>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="43">
         <v>9.0067660787175754</v>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="43">
         <v>9.4381734039746306</v>
       </c>
-      <c r="E8" s="45">
+      <c r="E8" s="44">
         <v>6.6444694450976713E-2</v>
       </c>
-      <c r="F8" s="44">
+      <c r="F8" s="43">
         <v>-1.5003089904785014</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="43">
         <v>3.1083931911108161E-3</v>
       </c>
       <c r="I8" s="12" t="s">
@@ -11692,26 +12708,26 @@
       <c r="P8"/>
       <c r="Q8"/>
     </row>
-    <row r="9" spans="1:17" s="44" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="44" t="s">
+    <row r="9" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="44">
+      <c r="B9" s="43">
         <v>2007</v>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="43">
         <v>9.0215195126889256</v>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="43">
         <v>15.504805342889711</v>
       </c>
-      <c r="E9" s="45">
+      <c r="E9" s="44">
         <v>4.9130083840008838E-2</v>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="43">
         <v>1.0286102294922017</v>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="43">
         <v>3.1997266934576897E-3</v>
       </c>
       <c r="I9"/>
@@ -11724,26 +12740,26 @@
       <c r="P9"/>
       <c r="Q9"/>
     </row>
-    <row r="10" spans="1:17" s="44" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="44" t="s">
+    <row r="10" spans="1:17" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="44">
+      <c r="B10" s="43">
         <v>2008</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="43">
         <v>1.8634834546203507</v>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="43">
         <v>10.755848390317652</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="44">
         <v>8.1254097124981689E-2</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="43">
         <v>2.6227378845214986</v>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="43">
         <v>1.853138513696757E-2</v>
       </c>
       <c r="I10" t="s">
@@ -11758,26 +12774,26 @@
       <c r="P10"/>
       <c r="Q10"/>
     </row>
-    <row r="11" spans="1:17" s="44" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="44" t="s">
+    <row r="11" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="44">
+      <c r="B11" s="43">
         <v>2009</v>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="43">
         <v>0.1279533827780881</v>
       </c>
-      <c r="D11" s="44">
+      <c r="D11" s="43">
         <v>5.4869663539406588</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="44">
         <v>1.5944602852234029E-2</v>
       </c>
-      <c r="F11" s="44">
+      <c r="F11" s="43">
         <v>0.32201004028320313</v>
       </c>
-      <c r="G11" s="44">
+      <c r="G11" s="43">
         <v>-1.8600894741257219E-2</v>
       </c>
       <c r="I11" s="13"/>
@@ -11800,26 +12816,26 @@
       <c r="P11"/>
       <c r="Q11"/>
     </row>
-    <row r="12" spans="1:17" s="44" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="44" t="s">
+    <row r="12" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="44">
+      <c r="B12" s="43">
         <v>2010</v>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="43">
         <v>14.519749710899404</v>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="43">
         <v>6.7504864541236316</v>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="44">
         <v>5.4276356944440586E-2</v>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="43">
         <v>5.7464294433593963</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="43">
         <v>3.1726488987337619E-2</v>
       </c>
       <c r="I12" t="s">
@@ -11844,26 +12860,26 @@
       <c r="P12"/>
       <c r="Q12"/>
     </row>
-    <row r="13" spans="1:17" s="44" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="44" t="s">
+    <row r="13" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="44">
+      <c r="B13" s="43">
         <v>2011</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="43">
         <v>6.2149341685898918</v>
       </c>
-      <c r="D13" s="44">
+      <c r="D13" s="43">
         <v>6.3654496770575264</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="44">
         <v>2.822334970567561E-2</v>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="43">
         <v>0.45959091186520595</v>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="43">
         <v>0.11578928480643602</v>
       </c>
       <c r="I13" t="s">
@@ -11884,26 +12900,26 @@
       <c r="P13"/>
       <c r="Q13"/>
     </row>
-    <row r="14" spans="1:17" s="44" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="44" t="s">
+    <row r="14" spans="1:17" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="44">
+      <c r="B14" s="43">
         <v>2012</v>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="43">
         <v>4.4354975937853709</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="43">
         <v>8.6296671918287444</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="44">
         <v>3.943479121375297E-2</v>
       </c>
-      <c r="F14" s="44">
+      <c r="F14" s="43">
         <v>1.747440338134794</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="43">
         <v>-1.1007246851475E-2</v>
       </c>
       <c r="I14" s="12" t="s">
@@ -11922,26 +12938,26 @@
       <c r="P14"/>
       <c r="Q14"/>
     </row>
-    <row r="15" spans="1:17" s="44" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="44" t="s">
+    <row r="15" spans="1:17" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="44">
+      <c r="B15" s="43">
         <v>2013</v>
       </c>
-      <c r="C15" s="44">
+      <c r="C15" s="43">
         <v>4.8176309912067552</v>
       </c>
-      <c r="D15" s="44">
+      <c r="D15" s="43">
         <v>6.1589019003012169</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="44">
         <v>1.5674084073140655E-2</v>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="43">
         <v>1.3192596435547017</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="43">
         <v>-2.3834748944580014E-2</v>
       </c>
       <c r="I15"/>
@@ -11954,33 +12970,33 @@
       <c r="P15"/>
       <c r="Q15"/>
     </row>
-    <row r="16" spans="1:17" s="44" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="44" t="s">
+    <row r="16" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="44">
+      <c r="B16" s="43">
         <v>2014</v>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="43">
         <v>3.9355402770900696</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="43">
         <v>4.2202416729045353</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="44">
         <v>2.8839824563956423E-2</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="43">
         <v>1.1507110595702983</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="43">
         <v>-1.4579980356545993E-2</v>
       </c>
       <c r="I16" s="13"/>
-      <c r="J16" s="46" t="s">
+      <c r="J16" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="K16" s="46" t="s">
+      <c r="K16" s="45" t="s">
         <v>121</v>
       </c>
       <c r="L16" s="13" t="s">
@@ -12002,26 +13018,26 @@
         <v>139</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="44" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="44" t="s">
+    <row r="17" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="44">
+      <c r="B17" s="43">
         <v>2015</v>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="43">
         <v>2.9767993163480639</v>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="43">
         <v>1.9600159921878912</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="44">
         <v>2.8067545081224287E-2</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="43">
         <v>0.8884201049804048</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="43">
         <v>-7.048831203233541E-2</v>
       </c>
       <c r="I17" t="s">
@@ -12052,26 +13068,26 @@
         <v>3.6188667293148882</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="44" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="44" t="s">
+    <row r="18" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="44">
+      <c r="B18" s="43">
         <v>2016</v>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="43">
         <v>3.7475784879279246</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="43">
         <v>0.53248385761912687</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="44">
         <v>7.7097953393005167E-3</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="43">
         <v>0.74551773071289773</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="43">
         <v>-5.0371849744336034E-3</v>
       </c>
       <c r="I18">
@@ -12102,26 +13118,26 @@
         <v>0.46286742114136015</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="44" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="44" t="s">
+    <row r="19" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="44">
+      <c r="B19" s="43">
         <v>2017</v>
       </c>
-      <c r="C19" s="44">
+      <c r="C19" s="43">
         <v>4.4768991584587638</v>
       </c>
-      <c r="D19" s="44">
+      <c r="D19" s="43">
         <v>5.1105018859230142</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="44">
         <v>-3.6148977192293381E-3</v>
       </c>
-      <c r="F19" s="44">
+      <c r="F19" s="43">
         <v>1.4455909729003977</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="43">
         <v>-2.8901083437207382E-2</v>
       </c>
       <c r="I19">
@@ -12152,26 +13168,26 @@
         <v>64.721430858297609</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="44" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="44" t="s">
+    <row r="20" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="44">
+      <c r="B20" s="43">
         <v>2018</v>
       </c>
-      <c r="C20" s="44">
+      <c r="C20" s="43">
         <v>3.4519759658686979</v>
       </c>
-      <c r="D20" s="44">
+      <c r="D20" s="43">
         <v>-4.9559467749032819</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="44">
         <v>6.652606309509511E-3</v>
       </c>
-      <c r="F20" s="44">
+      <c r="F20" s="43">
         <v>1.5284996032715057</v>
       </c>
-      <c r="G20" s="44">
+      <c r="G20" s="43">
         <v>-2.6412172896658097E-4</v>
       </c>
       <c r="I20">
@@ -12202,26 +13218,26 @@
         <v>2.896543407993434</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="44" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="44" t="s">
+    <row r="21" spans="1:17" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="44">
+      <c r="B21" s="43">
         <v>2019</v>
       </c>
-      <c r="C21" s="44">
+      <c r="C21" s="43">
         <v>1.3080411815312658</v>
       </c>
-      <c r="D21" s="44">
+      <c r="D21" s="43">
         <v>2.4854345450697792</v>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="44">
         <v>2.4254323011358346E-2</v>
       </c>
-      <c r="F21" s="44">
+      <c r="F21" s="43">
         <v>1.4892921447753977</v>
       </c>
-      <c r="G21" s="44">
+      <c r="G21" s="43">
         <v>-1.9500992509015986E-5</v>
       </c>
       <c r="I21" s="12">
@@ -12252,26 +13268,26 @@
         <v>63.08826787265825</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="44" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="44" t="s">
+    <row r="22" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="44">
+      <c r="B22" s="43">
         <v>2020</v>
       </c>
-      <c r="C22" s="44">
+      <c r="C22" s="43">
         <v>-3.8147088551071278</v>
       </c>
-      <c r="D22" s="44">
+      <c r="D22" s="43">
         <v>-14.036826610500484</v>
       </c>
-      <c r="E22" s="45">
+      <c r="E22" s="44">
         <v>-1.6889283404655522E-2</v>
       </c>
-      <c r="F22" s="44">
+      <c r="F22" s="43">
         <v>1.0362510681151988</v>
       </c>
-      <c r="G22" s="44">
+      <c r="G22" s="43">
         <v>7.2806108127268987E-5</v>
       </c>
       <c r="I22"/>
@@ -12284,26 +13300,26 @@
       <c r="P22"/>
       <c r="Q22"/>
     </row>
-    <row r="23" spans="1:17" s="44" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="44" t="s">
+    <row r="23" spans="1:17" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="44">
+      <c r="B23" s="43">
         <v>2021</v>
       </c>
-      <c r="C23" s="44">
+      <c r="C23" s="43">
         <v>9.7568044629903028</v>
       </c>
-      <c r="D23" s="44">
+      <c r="D23" s="43">
         <v>23.19530166138037</v>
       </c>
-      <c r="E23" s="45">
+      <c r="E23" s="44">
         <v>-1.878298325607505E-2</v>
       </c>
-      <c r="F23" s="44">
+      <c r="F23" s="43">
         <v>3.5513191223145029</v>
       </c>
-      <c r="G23" s="44">
+      <c r="G23" s="43">
         <v>-6.1083159356694992E-5</v>
       </c>
       <c r="I23"/>
@@ -12316,7 +13332,7 @@
       <c r="P23"/>
       <c r="Q23"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -12329,14 +13345,14 @@
       <c r="D24">
         <v>4.6836003157948483</v>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="42">
         <v>3.285579637489322E-2</v>
       </c>
       <c r="F24" s="25">
         <v>1.2494697570800994</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>75</v>
       </c>
@@ -12349,11 +13365,11 @@
       <c r="D25">
         <v>-0.90499801575536765</v>
       </c>
-      <c r="E25" s="43">
+      <c r="E25" s="42">
         <v>4.8846829878268612E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -12366,11 +13382,11 @@
       <c r="D26">
         <v>2.9363431733128351</v>
       </c>
-      <c r="E26" s="43">
+      <c r="E26" s="42">
         <v>2.5948693402780471E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>113</v>
       </c>
@@ -12381,17 +13397,17 @@
         <v>4.0059049215621823</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>159</v>
       </c>
@@ -12405,19 +13421,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F09706D3-3ACC-423F-8903-C5F506436891}">
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.19921875" style="9" customWidth="1"/>
-    <col min="2" max="2" width="9.06640625" style="43"/>
-    <col min="3" max="3" width="13.33203125" style="25" customWidth="1"/>
-    <col min="6" max="6" width="35.9296875" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9" style="42"/>
+    <col min="3" max="3" width="13.28515625" style="25" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" ht="105" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="41" t="s">
         <v>160</v>
       </c>
       <c r="C1" s="40" t="s">
@@ -12430,11 +13446,11 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>2.2151140569329326E-2</v>
       </c>
-      <c r="B2" s="43">
+      <c r="B2" s="42">
         <v>2.6196426063287068E-2</v>
       </c>
       <c r="C2" s="25">
@@ -12444,11 +13460,11 @@
         <v>11.921913382779238</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>3.9161122076016859E-2</v>
       </c>
-      <c r="B3" s="43">
+      <c r="B3" s="42">
         <v>0.10095789952110516</v>
       </c>
       <c r="C3" s="25">
@@ -12462,11 +13478,11 @@
       </c>
       <c r="G3" s="14"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>-5.7913549410153149E-2</v>
       </c>
-      <c r="B4" s="43">
+      <c r="B4" s="42">
         <v>2.4327664374301224E-2</v>
       </c>
       <c r="C4" s="25">
@@ -12482,11 +13498,11 @@
         <v>0.90255618496708157</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>-1.4434910115454443E-2</v>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="42">
         <v>3.8314156675365557E-2</v>
       </c>
       <c r="C5" s="25">
@@ -12498,15 +13514,15 @@
       <c r="F5" t="s">
         <v>119</v>
       </c>
-      <c r="G5" s="47">
+      <c r="G5" s="46">
         <v>0.81460766702233278</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>8.6240329270084265E-2</v>
       </c>
-      <c r="B6" s="43">
+      <c r="B6" s="42">
         <v>1.2547476294674259E-2</v>
       </c>
       <c r="C6" s="25">
@@ -12522,11 +13538,11 @@
         <v>0.77182482095056337</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>3.299476907418445E-2</v>
       </c>
-      <c r="B7" s="43">
+      <c r="B7" s="42">
         <v>3.4458609673707216E-2</v>
       </c>
       <c r="C7" s="25">
@@ -12542,11 +13558,11 @@
         <v>1.9437792621639249E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>4.7335193758095443E-3</v>
       </c>
-      <c r="B8" s="43">
+      <c r="B8" s="42">
         <v>4.5084002479668366E-2</v>
       </c>
       <c r="C8" s="25">
@@ -12558,15 +13574,15 @@
       <c r="F8" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="47">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>3.2000645038203282E-2</v>
       </c>
-      <c r="B9" s="43">
+      <c r="B9" s="42">
         <v>4.5206366540080929E-2</v>
       </c>
       <c r="C9" s="25">
@@ -12576,11 +13592,11 @@
         <v>1.6712764155420388</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>1.0220811788075115E-2</v>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="42">
         <v>1.298801994834551E-2</v>
       </c>
       <c r="C10" s="25">
@@ -12593,11 +13609,11 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>1.6540236975596098E-3</v>
       </c>
-      <c r="B11" s="43">
+      <c r="B11" s="42">
         <v>-8.2362148283519395E-3</v>
       </c>
       <c r="C11" s="25">
@@ -12623,11 +13639,11 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>2.9538255634357968E-2</v>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="42">
         <v>-2.3667099140445851E-3</v>
       </c>
       <c r="C12" s="25">
@@ -12655,11 +13671,11 @@
         <v>4.8672019036150807E-5</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>4.8559426664513565E-2</v>
       </c>
-      <c r="B13" s="43">
+      <c r="B13" s="42">
         <v>5.4918441126029546E-2</v>
       </c>
       <c r="C13" s="25">
@@ -12681,11 +13697,11 @@
         <v>3.7782778200185326E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>2.7682989319762721E-2</v>
       </c>
-      <c r="B14" s="43">
+      <c r="B14" s="42">
         <v>-5.5840588606452392E-2</v>
       </c>
       <c r="C14" s="25">
@@ -12707,11 +13723,11 @@
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>-1.0909313190100821E-2</v>
       </c>
-      <c r="B15" s="43">
+      <c r="B15" s="42">
         <v>5.8581391931573521E-4</v>
       </c>
       <c r="C15" s="25">
@@ -12721,11 +13737,11 @@
         <v>-1.4550979032228923</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>-2.1623002157920537E-2</v>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="42">
         <v>-0.12560028144945354</v>
       </c>
       <c r="C16" s="25">
@@ -12760,11 +13776,11 @@
         <v>139</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>0.11857828176694038</v>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="42">
         <v>0.25553572307777783</v>
       </c>
       <c r="C17" s="25">
@@ -12801,11 +13817,11 @@
         <v>1.2140787778921209E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>7.9625886243627955E-3</v>
       </c>
-      <c r="B18" s="43">
+      <c r="B18" s="42">
         <v>1.3535487559950652E-2</v>
       </c>
       <c r="C18" s="25">
@@ -12842,7 +13858,7 @@
         <v>0.42349155312422504</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F19" t="s">
         <v>154</v>
       </c>
@@ -12871,7 +13887,7 @@
         <v>6.9061930286152835E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F20" s="12" t="s">
         <v>71</v>
       </c>
@@ -12909,7 +13925,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{889850B5-D3B7-45EF-87FA-2DEE08221817}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12920,13 +13936,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.796875" customWidth="1"/>
-    <col min="2" max="16" width="50.796875" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="16" width="50.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -12976,7 +13992,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13023,7 +14039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -13070,7 +14086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -13114,7 +14130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -13158,7 +14174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -13202,7 +14218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -13252,7 +14268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>95</v>
       </c>
@@ -13302,7 +14318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>76</v>
       </c>
@@ -13352,7 +14368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>64</v>
       </c>
@@ -13402,7 +14418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -13452,7 +14468,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -13499,7 +14515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -13546,7 +14562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>

--- a/ECON251/Tutorial/T01/Assignment 1 template (To submit on Moodle) .xlsx
+++ b/ECON251/Tutorial/T01/Assignment 1 template (To submit on Moodle) .xlsx
@@ -5,25 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ECON251\Tutorial\T01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4194DFE3-4B0E-4C89-B4C2-AFBAB98626AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA06AC11-AC18-4652-98EF-D7DCBA282024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Country Assigned" sheetId="16" r:id="rId2"/>
     <sheet name="sg" sheetId="10" r:id="rId3"/>
-    <sheet name="regression 1 _SG" sheetId="11" r:id="rId4"/>
-    <sheet name="regression 2_SG" sheetId="12" r:id="rId5"/>
-    <sheet name="regression 3_sg" sheetId="17" r:id="rId6"/>
-    <sheet name="SG_Charts " sheetId="13" r:id="rId7"/>
-    <sheet name="Series - Metadata" sheetId="2" r:id="rId8"/>
+    <sheet name="sg_charts_test" sheetId="18" r:id="rId4"/>
+    <sheet name="regression 1 _SG" sheetId="11" r:id="rId5"/>
+    <sheet name="regression 2_SG" sheetId="12" r:id="rId6"/>
+    <sheet name="regression 3_sg" sheetId="17" r:id="rId7"/>
+    <sheet name="SG_Charts " sheetId="13" r:id="rId8"/>
+    <sheet name="Series - Metadata" sheetId="2" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -654,7 +655,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000%"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -816,7 +817,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -974,11 +975,8 @@
     <xf numFmtId="10" fontId="5" fillId="10" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -987,8 +985,8 @@
     <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1009,6 +1007,5823 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Chart 4. Manufacturing Value Added vs Employment in Agriculture in Singapore (2000–2024)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sg!$W$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Employment in agriculture (% of total employment) (modeled ILO estimate)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.910719427163002E-4"/>
+                  <c:y val="-6.3599568348091592E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>sg!$T$2:$T$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="1">
+                  <c:v>15.146298038161788</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-11.605048125430017</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.4686746225800107</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9963638945377227</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13.8458129716023</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.5096402529214856</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.921913382779238</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.9408665704516324</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4.1884694683058541</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-4.1502986226508227</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>29.675335626760187</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.8077670717552081</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.31910712270446595</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.6712764155420388</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.6831203913080088</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-5.1278017991461269</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.7010008068074569</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10.406115334791167</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.0287004412821261</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-1.4550979032228923</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7.5307063016974496</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>13.303540009852924</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.6997624563978491</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-4.2302587923025925</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.2628399445695493</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>sg!$W$2:$W$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="1">
+                  <c:v>0.17689908365402099</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.173741005150197</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.16944763175838501</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.16459654177274699</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.15970081754349399</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.155212233759282</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.15069969562712299</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.14645508484910399</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.14231124802675299</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.13906365808080101</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.13561924621409599</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13246039834856399</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.12955873329242601</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.12679854020966699</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.124092213197688</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.12145966005548101</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.11897925916280699</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.117077595142899</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.115089283007242</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.113041897035994</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.108162685533748</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.107777556138585</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9.0952445633474793E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7.9580186024164501E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.7983733027354095E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-96F2-4C5D-9E67-19110D0AEEE6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1988436575"/>
+        <c:axId val="1793359567"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1988436575"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Manufacturing (% of GDP)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1793359567"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1793359567"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Employment in Agriculture (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1988436575"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Chart 3. Trends in Singapore's Sectoral Growth (2000–2024)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sg!$AD$1:$AD$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>General government final consumption expenditure (% of GDP) [NE.CON.GOVT.ZS]</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>G</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>sg!$B$3:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$AD$3:$AD$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>10.504164644115525</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.609926556509718</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.84032888729563</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.4140839970397</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.318670184588006</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.8971432332187881</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.9069355027210513</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.1361273439883615</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.113213911286202</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.9299738486408202</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.6915683859659953</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.2368426370194889</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.8578668846884447</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9.7442177273746502</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9.6310320219758019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>10.19090831587924</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10.200372971650724</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10.140018759338188</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9.9398348941138064</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>10.253396494246401</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>12.190147791383446</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>10.532697743092175</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9.1289494952629333</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9.8421032695316715</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>10.05318763287927</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-4C3E-4CBF-896D-A8BE7936E744}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sg!$AE$1:$AE$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Households and NPISHs final consumption expenditure (% of GDP) [NE.CON.PRVT.ZS]</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>sg!$B$3:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$AE$3:$AE$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>41.855216732958041</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46.244971582292017</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46.182484892705467</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45.535361064297177</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>41.998426193084512</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>39.847877286424129</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>38.106096406316425</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36.765963470158894</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>39.95092384654248</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>39.102921622057082</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>36.337838296581353</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>36.615610020152666</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>37.306048070547945</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37.333460129295503</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>37.584381318964205</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>37.158080606153213</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>36.336754045415525</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>35.184722354653985</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>34.614491407338598</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>35.845393881281687</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>32.147432325908682</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>28.780240455600087</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>28.099108159151914</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>31.513116296958909</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>30.684280484260235</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-4C3E-4CBF-896D-A8BE7936E744}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sg!$AF$1:$AF$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Gross fixed capital formation (% of GDP) [NE.GDI.FTOT.ZS]</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>I</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>sg!$B$3:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$AF$3:$AF$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>32.326344362576407</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.887040232314138</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>26.751423220905973</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24.766294434624459</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24.281423420921346</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23.187995656323011</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23.086711145212458</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>24.375682074209674</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>27.978919594541324</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28.837459653073982</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>25.569721215450116</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25.264914637905171</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>26.429988298955582</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>27.548215593668829</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>28.128209222306971</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>27.222270897150295</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>25.877029477577924</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>25.115649681750725</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>22.351805620065026</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>22.799478885505962</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20.999459350147131</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22.078228221894115</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>20.338964403941983</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>21.87302410554809</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21.037456033494557</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-4C3E-4CBF-896D-A8BE7936E744}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>External balance on goods and services (% of GDP)</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>sg!$B$3:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$AG$3:$AG$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>12.337260101284532</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.496255724564534</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.426222147387328</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.953848478026121</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26.379678346782697</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29.88882255327351</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30.711834579105247</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>31.270315543664491</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20.660826979180964</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>23.497058193413821</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>26.312365798407917</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>27.556785921536942</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>24.226259963852854</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>23.113812627266899</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>23.439752408773177</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>27.297818059101541</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26.253769658413212</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>26.545597667222111</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>29.700268952184881</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>29.367995967723893</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>31.279400415186071</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>35.785344863952751</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>39.774395154749833</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>37.158805824026295</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>36.012331849548822</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-4C3E-4CBF-896D-A8BE7936E744}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sg!$S$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Manufacturing, value added (% of GDP)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.3638858688095178E-2"/>
+                  <c:y val="-0.15563538932633419"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$S$2:$S$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="1">
+                  <c:v>25.861486037755899</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23.394697847414562</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24.737640322972926</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24.765412693196893</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27.119367597064286</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>27.076761798207059</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>26.578005985802772</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>23.822651904527213</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.585664973848445</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.273376429073512</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.773833025312548</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>19.582551507977822</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>19.116821980066192</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17.638409614875453</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17.999768892128522</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18.089329854873405</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17.441961312599027</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18.545847537786003</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20.717845766781217</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>19.40403130191034</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>19.653984525036179</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>20.633068003561824</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>19.655537649937781</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>16.975559443779353</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>16.332704934853503</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4C3E-4CBF-896D-A8BE7936E744}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sg!$V$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Agriculture, forestry, and fishing, value added (% of GDP)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.7120969739025413E-2"/>
+                  <c:y val="-1.2160615339749199E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$V$2:$V$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="1">
+                  <c:v>9.2131732680321002E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.2356655909540694E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.1032800014001363E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.1134072311026647E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.5648989626246571E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.5048114214259862E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.8865424451682515E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.286799737144735E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.1432188466446869E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.0687761270138054E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.614898888342135E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.4607600751235389E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.3272726533169004E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.4375216793813404E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.4540851073536168E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.2613513802648333E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.1521289438126224E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.0763583755226389E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.0117148236328394E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.2252130199608528E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.281725211869508E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.0551368665513827E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.597731637364643E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.8849802007551339E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.7439170694473516E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-4C3E-4CBF-896D-A8BE7936E744}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1993291247"/>
+        <c:axId val="1793327407"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sg!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GDP growth (annual %)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.7688990387098401E-2"/>
+                  <c:y val="-9.6216097987751534E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>sg!$B$3:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$D$2:$D$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="1">
+                  <c:v>9.0383163255516337</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.0708627510044835</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.923360767020128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.5482554264322914</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.9399826843495731</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.366322392507584</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.0067660787175754</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.0215195126889256</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.8634834546203507</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.1279533827780881</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14.519749710899404</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.2149341685898918</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.4354975937853709</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.8176309912067552</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.9355402770900696</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.9767993163480639</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.7475784879279246</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.4768991584587638</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.4519759658686979</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.3080411815312658</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-3.8147088551071278</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9.7568044629903028</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.1080002189715117</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.8214069411538532</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.3880236246186541</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-4C3E-4CBF-896D-A8BE7936E744}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1993175711"/>
+        <c:axId val="1793337007"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1993291247"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1793327407"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1793327407"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>% of GDP</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1993291247"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1793337007"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>GDP Growth Rate (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1993175711"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1993175711"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1793337007"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="tr"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.64805527120459894"/>
+          <c:y val="0.1300462962962963"/>
+          <c:w val="0.33933102335886089"/>
+          <c:h val="0.81713619130941961"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Chart</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> 2 - </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Components</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> of Spending in Singapore</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sg!$AD$1:$AD$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>General government final consumption expenditure (% of GDP) [NE.CON.GOVT.ZS]</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>G</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.8818343855934782E-2"/>
+                  <c:y val="5.6785535878099112E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>sg!$B$3:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$AD$3:$AD$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>10.504164644115525</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.609926556509718</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.84032888729563</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.4140839970397</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.318670184588006</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.8971432332187881</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.9069355027210513</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.1361273439883615</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.113213911286202</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.9299738486408202</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.6915683859659953</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.2368426370194889</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.8578668846884447</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9.7442177273746502</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9.6310320219758019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>10.19090831587924</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10.200372971650724</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10.140018759338188</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9.9398348941138064</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>10.253396494246401</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>12.190147791383446</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>10.532697743092175</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9.1289494952629333</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9.8421032695316715</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>10.05318763287927</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1C63-4AE4-9458-1A8B2FCDD046}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sg!$AE$1:$AE$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Households and NPISHs final consumption expenditure (% of GDP) [NE.CON.PRVT.ZS]</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.13084831742213307"/>
+                  <c:y val="-8.4502717389564774E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>sg!$B$3:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$AE$3:$AE$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>41.855216732958041</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46.244971582292017</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46.182484892705467</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45.535361064297177</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>41.998426193084512</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>39.847877286424129</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>38.106096406316425</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36.765963470158894</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>39.95092384654248</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>39.102921622057082</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>36.337838296581353</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>36.615610020152666</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>37.306048070547945</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37.333460129295503</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>37.584381318964205</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>37.158080606153213</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>36.336754045415525</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>35.184722354653985</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>34.614491407338598</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>35.845393881281687</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>32.147432325908682</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>28.780240455600087</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>28.099108159151914</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>31.513116296958909</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>30.684280484260235</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1C63-4AE4-9458-1A8B2FCDD046}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sg!$AF$1:$AF$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Gross fixed capital formation (% of GDP) [NE.GDI.FTOT.ZS]</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>I</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.651153919996745E-2"/>
+                  <c:y val="3.5081414992940055E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>sg!$B$3:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$AF$3:$AF$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>32.326344362576407</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.887040232314138</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>26.751423220905973</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24.766294434624459</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24.281423420921346</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23.187995656323011</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23.086711145212458</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>24.375682074209674</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>27.978919594541324</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28.837459653073982</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>25.569721215450116</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25.264914637905171</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>26.429988298955582</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>27.548215593668829</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>28.128209222306971</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>27.222270897150295</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>25.877029477577924</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>25.115649681750725</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>22.351805620065026</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>22.799478885505962</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20.999459350147131</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22.078228221894115</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>20.338964403941983</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>21.87302410554809</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21.037456033494557</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-1C63-4AE4-9458-1A8B2FCDD046}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sg!$AG$1:$AG$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>External balance on goods and services (% of GDP) [NE.RSB.GNFS.ZS]</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>NX</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.5114289456031848E-3"/>
+                  <c:y val="-8.8392353966317561E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>sg!$B$3:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$AG$3:$AG$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>12.337260101284532</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.496255724564534</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.426222147387328</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.953848478026121</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26.379678346782697</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29.88882255327351</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30.711834579105247</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>31.270315543664491</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20.660826979180964</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>23.497058193413821</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>26.312365798407917</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>27.556785921536942</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>24.226259963852854</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>23.113812627266899</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>23.439752408773177</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>27.297818059101541</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26.253769658413212</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>26.545597667222111</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>29.700268952184881</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>29.367995967723893</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>31.279400415186071</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>35.785344863952751</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>39.774395154749833</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>37.158805824026295</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>36.012331849548822</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-1C63-4AE4-9458-1A8B2FCDD046}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2074857712"/>
+        <c:axId val="1942972912"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2074857712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1942972912"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1942972912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>% of GDP</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2074857712"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="0"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="1"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="6"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="7"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="8"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.65050656158777909"/>
+          <c:y val="0.21236395714400635"/>
+          <c:w val="0.33565261047641692"/>
+          <c:h val="0.60803632034575683"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Chart 3. Trends in Singapore's Sectoral Growth (2000–2024)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Manufacturing</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.3638858688095178E-2"/>
+                  <c:y val="-0.15563538932633419"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>sg!$B$3:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$S$2:$S$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="1">
+                  <c:v>25.861486037755899</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23.394697847414562</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24.737640322972926</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24.765412693196893</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27.119367597064286</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>27.076761798207059</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>26.578005985802772</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>23.822651904527213</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.585664973848445</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.273376429073512</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.773833025312548</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>19.582551507977822</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>19.116821980066192</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17.638409614875453</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17.999768892128522</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18.089329854873405</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17.441961312599027</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18.545847537786003</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20.717845766781217</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>19.40403130191034</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>19.653984525036179</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>20.633068003561824</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>19.655537649937781</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>16.975559443779353</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>16.332704934853503</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-17BF-49D2-A3BD-172708BEC157}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Agriculture</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.7120969739025413E-2"/>
+                  <c:y val="-1.2160615339749199E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>sg!$B$3:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$V$2:$V$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="1">
+                  <c:v>9.2131732680321002E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.2356655909540694E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.1032800014001363E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.1134072311026647E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.5648989626246571E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.5048114214259862E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.8865424451682515E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.286799737144735E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.1432188466446869E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.0687761270138054E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.614898888342135E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.4607600751235389E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.3272726533169004E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.4375216793813404E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.4540851073536168E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.2613513802648333E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.1521289438126224E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.0763583755226389E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.0117148236328394E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.2252130199608528E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.281725211869508E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.0551368665513827E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.597731637364643E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.8849802007551339E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.7439170694473516E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-17BF-49D2-A3BD-172708BEC157}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1993291247"/>
+        <c:axId val="1793327407"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>GDP Growth</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.7688990387098401E-2"/>
+                  <c:y val="-9.6216097987751534E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>sg!$B$3:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sg!$D$2:$D$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="1">
+                  <c:v>9.0383163255516337</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.0708627510044835</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.923360767020128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.5482554264322914</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.9399826843495731</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.366322392507584</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.0067660787175754</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.0215195126889256</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.8634834546203507</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.1279533827780881</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14.519749710899404</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.2149341685898918</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.4354975937853709</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.8176309912067552</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.9355402770900696</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.9767993163480639</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.7475784879279246</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.4768991584587638</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.4519759658686979</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.3080411815312658</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-3.8147088551071278</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9.7568044629903028</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.1080002189715117</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.8214069411538532</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.3880236246186541</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-17BF-49D2-A3BD-172708BEC157}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1993175711"/>
+        <c:axId val="1793337007"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1993291247"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1793327407"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1793327407"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>% of GDP</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1993291247"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1793337007"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>GDP Growth Rate (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1993175711"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1993175711"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1793337007"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="tr"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.72731001041047616"/>
+          <c:y val="0.1300462962962963"/>
+          <c:w val="0.26007628802039984"/>
+          <c:h val="0.81713619130941961"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Chart 4. Manufacturing Value Added vs Employment in Agriculture in Singapore (2000–2024)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sg!$W$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Employment in agriculture (% of total employment) (modeled ILO estimate)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.910719427163002E-4"/>
+                  <c:y val="-6.3599568348091592E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>sg!$T$2:$T$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="1">
+                  <c:v>15.146298038161788</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-11.605048125430017</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.4686746225800107</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9963638945377227</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13.8458129716023</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.5096402529214856</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.921913382779238</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.9408665704516324</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4.1884694683058541</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-4.1502986226508227</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>29.675335626760187</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.8077670717552081</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.31910712270446595</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.6712764155420388</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.6831203913080088</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-5.1278017991461269</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.7010008068074569</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10.406115334791167</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.0287004412821261</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-1.4550979032228923</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7.5307063016974496</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>13.303540009852924</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.6997624563978491</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-4.2302587923025925</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.2628399445695493</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>sg!$W$2:$W$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="1">
+                  <c:v>0.17689908365402099</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.173741005150197</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.16944763175838501</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.16459654177274699</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.15970081754349399</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.155212233759282</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.15069969562712299</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.14645508484910399</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.14231124802675299</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.13906365808080101</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.13561924621409599</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13246039834856399</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.12955873329242601</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.12679854020966699</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.124092213197688</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.12145966005548101</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.11897925916280699</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.117077595142899</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.115089283007242</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.113041897035994</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.108162685533748</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.107777556138585</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9.0952445633474793E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7.9580186024164501E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.7983733027354095E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C3A2-4612-A30C-DD642C46579A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1988436575"/>
+        <c:axId val="1793359567"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1988436575"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Manufacturing (% of GDP)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1793359567"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1793359567"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Employment in Agriculture (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1988436575"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2345,7 +8160,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3689,7 +9504,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4610,7 +10425,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5318,8 +11133,168 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -5342,6 +11317,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
@@ -5437,7 +11423,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -5469,10 +11455,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -5793,6 +11779,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -7347,7 +13344,2524 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>295276</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1200150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32F89435-B88E-C02E-3F0C-384491F26861}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>134469</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>537883</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>156881</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14523182-98E8-4FFD-9DF2-CA48240DA2D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>582706</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>36980</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>136711</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C88526CD-CAFD-44E2-B182-450EDDDC433B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>358587</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>56029</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>470646</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B45F83AB-DB4D-C91B-E33D-E5FDBB129A5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13671175" y="246529"/>
+          <a:ext cx="6163236" cy="1804147"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000" b="1"/>
+            <a:t>Compare Chart 1 vs 2:</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="2000"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000"/>
+            <a:t>Chart 1 is better for seeing </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000" b="1"/>
+            <a:t>composition</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000"/>
+            <a:t> (what makes up GDP each year)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000"/>
+            <a:t>Chart 2 is better for seeing </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000" b="1"/>
+            <a:t>trends</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000"/>
+            <a:t> (which component is growing or shrinking)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>33616</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>168087</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>231914</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>74542</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35F3E062-F6F2-4096-880C-4DA39C4F7354}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>554934</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>173935</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>470646</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>56029</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B42A9B58-B9FF-43FA-ADC8-E7FF24F0E3DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="554934" y="8365435"/>
+          <a:ext cx="7782241" cy="2739594"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>The chart illustrates Singapore's structural transformation between 2000 and 2024.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>Manufacturing's share of GDP declined steadily, indicating a gradual shift away from</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>manufacturing towards a more service-oriented economy. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>Agriculture remained negligible throughout the period, reflecting Singapore's limited agricultural sector. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>Although GDP growth showed a slight downward trend, the very low R² value suggests that economic growth was highly volatile and influenced by cyclical and external factors rather than a consistent long-term trend.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>22411</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>267259</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>82643</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B6737CA-3886-4622-BE0A-4CF9287B962B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123264</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>520830</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>5358</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4A0052C-FC6E-4963-A015-15DA3ACE17FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9076765" y="9267264"/>
+          <a:ext cx="7782241" cy="2739594"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>The scatter plot shows a very weak positive relationship between manufacturing value added and employment in agriculture. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>The fitted linear trendline has a slope of 0.0005, indicating almost no meaningful change in agricultural employment as manufacturing's share of GDP changes. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>Furthermore, the R² value of 0.0214 suggests that manufacturing value added explains only about 2.1% of the variation in agricultural employment. Overall, there is little evidence of a significant linear relationship between these two variables in Singapore during 2000–2024.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -8779,64 +17293,64 @@
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="64" t="s">
+      <c r="H1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="64" t="s">
+      <c r="I1" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="J1" s="64" t="s">
+      <c r="J1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="64" t="s">
+      <c r="K1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="L1" s="64" t="s">
+      <c r="L1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="M1" s="64" t="s">
+      <c r="M1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="64" t="s">
+      <c r="N1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="O1" s="64" t="s">
+      <c r="O1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="64" t="s">
+      <c r="P1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="Q1" s="64" t="s">
+      <c r="Q1" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="R1" s="64" t="s">
+      <c r="R1" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="S1" s="64" t="s">
+      <c r="S1" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="T1" s="64" t="s">
+      <c r="T1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="U1" s="64" t="s">
+      <c r="U1" s="2" t="s">
         <v>164</v>
       </c>
     </row>
@@ -9007,15 +17521,15 @@
         <v>152</v>
       </c>
       <c r="U2" s="32"/>
-      <c r="V2" s="59" t="s">
+      <c r="V2" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="63"/>
+      <c r="Y2" s="63"/>
+      <c r="Z2" s="63"/>
+      <c r="AA2" s="63"/>
+      <c r="AB2" s="63"/>
       <c r="AC2" s="33"/>
       <c r="AD2" s="23" t="s">
         <v>148</v>
@@ -9230,6 +17744,7 @@
     <col min="16" max="16" width="9" style="49"/>
     <col min="17" max="17" width="15.5703125" customWidth="1"/>
     <col min="18" max="18" width="13.28515625" style="25" customWidth="1"/>
+    <col min="21" max="21" width="9.28515625" customWidth="1"/>
     <col min="25" max="25" width="14.85546875" style="25" customWidth="1"/>
     <col min="28" max="28" width="12" style="25" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="5.5703125" customWidth="1"/>
@@ -9393,13 +17908,13 @@
       <c r="B3" s="3">
         <v>2000</v>
       </c>
-      <c r="C3" s="60">
+      <c r="C3" s="59">
         <v>140533304238.72125</v>
       </c>
       <c r="D3">
         <v>9.0383163255516337</v>
       </c>
-      <c r="E3" s="60">
+      <c r="E3" s="59">
         <v>43703162220.646263</v>
       </c>
       <c r="F3">
@@ -9419,17 +17934,17 @@
         <f>(I3/100)*G3</f>
         <v>2058990.2999999998</v>
       </c>
-      <c r="K3" s="62"/>
-      <c r="L3" s="61">
+      <c r="K3" s="61"/>
+      <c r="L3" s="60">
         <f>C3/J3</f>
         <v>68253.504758483454</v>
       </c>
-      <c r="M3" s="63"/>
-      <c r="N3" s="61">
+      <c r="M3" s="62"/>
+      <c r="N3" s="60">
         <f>E3/J3</f>
         <v>21225.530892810068</v>
       </c>
-      <c r="O3" s="62"/>
+      <c r="O3" s="61"/>
       <c r="Q3" t="s">
         <v>169</v>
       </c>
@@ -9480,13 +17995,13 @@
       <c r="B4" s="3">
         <v>2001</v>
       </c>
-      <c r="C4" s="60">
+      <c r="C4" s="59">
         <v>139028385430.87299</v>
       </c>
       <c r="D4">
         <v>-1.0708627510044835</v>
       </c>
-      <c r="E4" s="60">
+      <c r="E4" s="59">
         <v>41427454403.287689</v>
       </c>
       <c r="F4">
@@ -9510,7 +18025,7 @@
         <f>((J4-J3)/J3)</f>
         <v>3.1078337377305879E-2</v>
       </c>
-      <c r="L4" s="61">
+      <c r="L4" s="60">
         <f t="shared" ref="L4:L27" si="2">C4/J4</f>
         <v>65487.364977061887</v>
       </c>
@@ -9518,7 +18033,7 @@
         <f>(L4-L3)/L3</f>
         <v>-4.0527439451052576E-2</v>
       </c>
-      <c r="N4" s="61">
+      <c r="N4" s="60">
         <f t="shared" ref="N4:N27" si="3">E4/J4</f>
         <v>19513.819556853177</v>
       </c>
@@ -9582,13 +18097,13 @@
       <c r="B5" s="3">
         <v>2002</v>
       </c>
-      <c r="C5" s="60">
+      <c r="C5" s="59">
         <v>144482970559.8894</v>
       </c>
       <c r="D5">
         <v>3.923360767020128</v>
       </c>
-      <c r="E5" s="60">
+      <c r="E5" s="59">
         <v>37635189933.264236</v>
       </c>
       <c r="F5">
@@ -9612,7 +18127,7 @@
         <f t="shared" ref="K5:K27" si="4">((J5-J4)/J4)</f>
         <v>-2.1927623777409942E-2</v>
       </c>
-      <c r="L5" s="61">
+      <c r="L5" s="60">
         <f t="shared" si="2"/>
         <v>69582.448309979532</v>
       </c>
@@ -9620,7 +18135,7 @@
         <f t="shared" ref="M5:M27" si="5">(L5-L4)/L4</f>
         <v>6.253241880097056E-2</v>
       </c>
-      <c r="N5" s="61">
+      <c r="N5" s="60">
         <f t="shared" si="3"/>
         <v>18124.964125665781</v>
       </c>
@@ -9684,13 +18199,13 @@
       <c r="B6" s="3">
         <v>2003</v>
       </c>
-      <c r="C6" s="60">
+      <c r="C6" s="59">
         <v>151054425108.65015</v>
       </c>
       <c r="D6">
         <v>4.5482554264322914</v>
       </c>
-      <c r="E6" s="60">
+      <c r="E6" s="59">
         <v>35694579310.094017</v>
       </c>
       <c r="F6">
@@ -9714,7 +18229,7 @@
         <f t="shared" si="4"/>
         <v>-1.4019524271750093E-2</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="60">
         <f t="shared" si="2"/>
         <v>73781.618989312294</v>
       </c>
@@ -9722,7 +18237,7 @@
         <f t="shared" si="5"/>
         <v>6.034813061802706E-2</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="60">
         <f t="shared" si="3"/>
         <v>17434.801057611206</v>
       </c>
@@ -9786,13 +18301,13 @@
       <c r="B7" s="3">
         <v>2004</v>
       </c>
-      <c r="C7" s="60">
+      <c r="C7" s="59">
         <v>166069208808.39377</v>
       </c>
       <c r="D7">
         <v>9.9399826843495731</v>
       </c>
-      <c r="E7" s="60">
+      <c r="E7" s="59">
         <v>39369010601.349266</v>
       </c>
       <c r="F7">
@@ -9816,7 +18331,7 @@
         <f t="shared" si="4"/>
         <v>1.6981685674058087E-2</v>
       </c>
-      <c r="L7" s="61">
+      <c r="L7" s="60">
         <f t="shared" si="2"/>
         <v>79761.022527479596</v>
       </c>
@@ -9824,7 +18339,7 @@
         <f t="shared" si="5"/>
         <v>8.1041912878510494E-2</v>
       </c>
-      <c r="N7" s="61">
+      <c r="N7" s="60">
         <f t="shared" si="3"/>
         <v>18908.457287116842</v>
       </c>
@@ -9888,13 +18403,13 @@
       <c r="B8" s="3">
         <v>2005</v>
       </c>
-      <c r="C8" s="60">
+      <c r="C8" s="59">
         <v>178302402123.90665</v>
       </c>
       <c r="D8">
         <v>7.366322392507584</v>
       </c>
-      <c r="E8" s="60">
+      <c r="E8" s="59">
         <v>40801992980.92485</v>
       </c>
       <c r="F8">
@@ -9918,7 +18433,7 @@
         <f t="shared" si="4"/>
         <v>4.3720826643852136E-2</v>
       </c>
-      <c r="L8" s="61">
+      <c r="L8" s="60">
         <f t="shared" si="2"/>
         <v>82049.21699779015</v>
       </c>
@@ -9926,7 +18441,7 @@
         <f t="shared" si="5"/>
         <v>2.8688128584638147E-2</v>
       </c>
-      <c r="N8" s="61">
+      <c r="N8" s="60">
         <f t="shared" si="3"/>
         <v>18775.807482996028</v>
       </c>
@@ -9990,13 +18505,13 @@
       <c r="B9" s="3">
         <v>2006</v>
       </c>
-      <c r="C9" s="60">
+      <c r="C9" s="59">
         <v>194361682395.94128</v>
       </c>
       <c r="D9">
         <v>9.0067660787175754</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E9" s="59">
         <v>44652955830.742096</v>
       </c>
       <c r="F9">
@@ -10020,7 +18535,7 @@
         <f t="shared" si="4"/>
         <v>6.6444694450976713E-2</v>
       </c>
-      <c r="L9" s="61">
+      <c r="L9" s="60">
         <f t="shared" si="2"/>
         <v>83866.700737111605</v>
       </c>
@@ -10028,7 +18543,7 @@
         <f t="shared" si="5"/>
         <v>2.2151140569329326E-2</v>
       </c>
-      <c r="N9" s="61">
+      <c r="N9" s="60">
         <f t="shared" si="3"/>
         <v>19267.666535502845</v>
       </c>
@@ -10095,13 +18610,13 @@
       <c r="B10" s="3">
         <v>2007</v>
       </c>
-      <c r="C10" s="60">
+      <c r="C10" s="59">
         <v>211896059498.4816</v>
       </c>
       <c r="D10">
         <v>9.0215195126889256</v>
       </c>
-      <c r="E10" s="60">
+      <c r="E10" s="59">
         <v>51576309712.14518</v>
       </c>
       <c r="F10">
@@ -10125,7 +18640,7 @@
         <f t="shared" si="4"/>
         <v>4.9130083840008838E-2</v>
       </c>
-      <c r="L10" s="61">
+      <c r="L10" s="60">
         <f t="shared" si="2"/>
         <v>87151.014842790406</v>
       </c>
@@ -10133,7 +18648,7 @@
         <f t="shared" si="5"/>
         <v>3.9161122076016859E-2</v>
       </c>
-      <c r="N10" s="61">
+      <c r="N10" s="60">
         <f t="shared" si="3"/>
         <v>21212.889677600302</v>
       </c>
@@ -10200,13 +18715,13 @@
       <c r="B11" s="3">
         <v>2008</v>
       </c>
-      <c r="C11" s="60">
+      <c r="C11" s="59">
         <v>215844707508.2283</v>
       </c>
       <c r="D11">
         <v>1.8634834546203507</v>
       </c>
-      <c r="E11" s="60">
+      <c r="E11" s="59">
         <v>57123779390.104187</v>
       </c>
       <c r="F11">
@@ -10230,7 +18745,7 @@
         <f t="shared" si="4"/>
         <v>8.1254097124981689E-2</v>
       </c>
-      <c r="L11" s="61">
+      <c r="L11" s="60">
         <f t="shared" si="2"/>
         <v>82103.790238547474</v>
       </c>
@@ -10238,7 +18753,7 @@
         <f t="shared" si="5"/>
         <v>-5.7913549410153149E-2</v>
       </c>
-      <c r="N11" s="61">
+      <c r="N11" s="60">
         <f t="shared" si="3"/>
         <v>21728.949738086041</v>
       </c>
@@ -10305,13 +18820,13 @@
       <c r="B12" s="3">
         <v>2009</v>
       </c>
-      <c r="C12" s="60">
+      <c r="C12" s="59">
         <v>216120888113.03256</v>
       </c>
       <c r="D12">
         <v>0.1279533827780881</v>
       </c>
-      <c r="E12" s="60">
+      <c r="E12" s="59">
         <v>60258141945.338493</v>
       </c>
       <c r="F12">
@@ -10335,7 +18850,7 @@
         <f t="shared" si="4"/>
         <v>1.5944602852234029E-2</v>
       </c>
-      <c r="L12" s="61">
+      <c r="L12" s="60">
         <f t="shared" si="2"/>
         <v>80918.629406315915</v>
       </c>
@@ -10343,7 +18858,7 @@
         <f t="shared" si="5"/>
         <v>-1.4434910115454443E-2</v>
       </c>
-      <c r="N12" s="61">
+      <c r="N12" s="60">
         <f t="shared" si="3"/>
         <v>22561.476122742213</v>
       </c>
@@ -10410,13 +18925,13 @@
       <c r="B13" s="3">
         <v>2010</v>
       </c>
-      <c r="C13" s="60">
+      <c r="C13" s="59">
         <v>247501100140.01782</v>
       </c>
       <c r="D13">
         <v>14.519749710899404</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E13" s="59">
         <v>64325859654.865166</v>
       </c>
       <c r="F13">
@@ -10440,7 +18955,7 @@
         <f t="shared" si="4"/>
         <v>5.4276356944440586E-2</v>
       </c>
-      <c r="L13" s="61">
+      <c r="L13" s="60">
         <f t="shared" si="2"/>
         <v>87897.078650400523</v>
       </c>
@@ -10448,7 +18963,7 @@
         <f t="shared" si="5"/>
         <v>8.6240329270084265E-2</v>
       </c>
-      <c r="N13" s="61">
+      <c r="N13" s="60">
         <f t="shared" si="3"/>
         <v>22844.56570956518</v>
       </c>
@@ -10515,13 +19030,13 @@
       <c r="B14" s="3">
         <v>2011</v>
       </c>
-      <c r="C14" s="60">
+      <c r="C14" s="59">
         <v>262883130580.25568</v>
       </c>
       <c r="D14">
         <v>6.2149341685898918</v>
       </c>
-      <c r="E14" s="60">
+      <c r="E14" s="59">
         <v>68420489880.530258</v>
       </c>
       <c r="F14">
@@ -10545,7 +19060,7 @@
         <f t="shared" si="4"/>
         <v>2.822334970567561E-2</v>
       </c>
-      <c r="L14" s="61">
+      <c r="L14" s="60">
         <f t="shared" si="2"/>
         <v>90797.222462765916</v>
       </c>
@@ -10553,7 +19068,7 @@
         <f t="shared" si="5"/>
         <v>3.299476907418445E-2</v>
       </c>
-      <c r="N14" s="61">
+      <c r="N14" s="60">
         <f t="shared" si="3"/>
         <v>23631.757682516443</v>
       </c>
@@ -10620,13 +19135,13 @@
       <c r="B15" s="3">
         <v>2012</v>
       </c>
-      <c r="C15" s="60">
+      <c r="C15" s="59">
         <v>274543305511.61057</v>
       </c>
       <c r="D15">
         <v>4.4354975937853709</v>
       </c>
-      <c r="E15" s="60">
+      <c r="E15" s="59">
         <v>74324950448.238876</v>
       </c>
       <c r="F15">
@@ -10650,7 +19165,7 @@
         <f t="shared" si="4"/>
         <v>3.943479121375297E-2</v>
       </c>
-      <c r="L15" s="61">
+      <c r="L15" s="60">
         <f t="shared" si="2"/>
         <v>91227.012874563108</v>
       </c>
@@ -10658,7 +19173,7 @@
         <f t="shared" si="5"/>
         <v>4.7335193758095443E-3</v>
       </c>
-      <c r="N15" s="61">
+      <c r="N15" s="60">
         <f t="shared" si="3"/>
         <v>24697.171904473937</v>
       </c>
@@ -10725,13 +19240,13 @@
       <c r="B16" s="3">
         <v>2013</v>
       </c>
-      <c r="C16" s="60">
+      <c r="C16" s="59">
         <v>287769788882.22137</v>
       </c>
       <c r="D16">
         <v>4.8176309912067552</v>
       </c>
-      <c r="E16" s="60">
+      <c r="E16" s="59">
         <v>78902551233.793396</v>
       </c>
       <c r="F16">
@@ -10755,7 +19270,7 @@
         <f t="shared" si="4"/>
         <v>1.5674084073140655E-2</v>
       </c>
-      <c r="L16" s="61">
+      <c r="L16" s="60">
         <f t="shared" si="2"/>
         <v>94146.336131457603</v>
       </c>
@@ -10763,7 +19278,7 @@
         <f t="shared" si="5"/>
         <v>3.2000645038203282E-2</v>
       </c>
-      <c r="N16" s="61">
+      <c r="N16" s="60">
         <f t="shared" si="3"/>
         <v>25813.641310090974</v>
       </c>
@@ -10830,13 +19345,13 @@
       <c r="B17" s="3">
         <v>2014</v>
       </c>
-      <c r="C17" s="60">
+      <c r="C17" s="59">
         <v>299095084828.97827</v>
       </c>
       <c r="D17">
         <v>3.9355402770900696</v>
       </c>
-      <c r="E17" s="60">
+      <c r="E17" s="59">
         <v>82232429581.946793</v>
       </c>
       <c r="F17">
@@ -10860,7 +19375,7 @@
         <f t="shared" si="4"/>
         <v>2.8839824563956423E-2</v>
       </c>
-      <c r="L17" s="61">
+      <c r="L17" s="60">
         <f t="shared" si="2"/>
         <v>95108.588113594087</v>
       </c>
@@ -10868,7 +19383,7 @@
         <f t="shared" si="5"/>
         <v>1.0220811788075115E-2</v>
       </c>
-      <c r="N17" s="61">
+      <c r="N17" s="60">
         <f t="shared" si="3"/>
         <v>26148.909398365871</v>
       </c>
@@ -10935,13 +19450,13 @@
       <c r="B18" s="3">
         <v>2015</v>
       </c>
-      <c r="C18" s="60">
+      <c r="C18" s="59">
         <v>307998545269.39795</v>
       </c>
       <c r="D18">
         <v>2.9767993163480639</v>
       </c>
-      <c r="E18" s="60">
+      <c r="E18" s="59">
         <v>83844198352.517593</v>
       </c>
       <c r="F18">
@@ -10965,7 +19480,7 @@
         <f t="shared" si="4"/>
         <v>2.8067545081224287E-2</v>
       </c>
-      <c r="L18" s="61">
+      <c r="L18" s="60">
         <f t="shared" si="2"/>
         <v>95265.899972175408</v>
       </c>
@@ -10973,7 +19488,7 @@
         <f t="shared" si="5"/>
         <v>1.6540236975596098E-3</v>
       </c>
-      <c r="N18" s="61">
+      <c r="N18" s="60">
         <f t="shared" si="3"/>
         <v>25933.541363033819</v>
       </c>
@@ -11040,13 +19555,13 @@
       <c r="B19" s="3">
         <v>2016</v>
       </c>
-      <c r="C19" s="60">
+      <c r="C19" s="59">
         <v>319541032495.04486</v>
       </c>
       <c r="D19">
         <v>3.7475784879279246</v>
       </c>
-      <c r="E19" s="60">
+      <c r="E19" s="59">
         <v>84290655174.294907</v>
       </c>
       <c r="F19">
@@ -11070,7 +19585,7 @@
         <f t="shared" si="4"/>
         <v>7.7097953393005167E-3</v>
       </c>
-      <c r="L19" s="61">
+      <c r="L19" s="60">
         <f t="shared" si="2"/>
         <v>98079.888478790701</v>
       </c>
@@ -11078,7 +19593,7 @@
         <f t="shared" si="5"/>
         <v>2.9538255634357968E-2</v>
       </c>
-      <c r="N19" s="61">
+      <c r="N19" s="60">
         <f t="shared" si="3"/>
         <v>25872.164193583641</v>
       </c>
@@ -11145,13 +19660,13 @@
       <c r="B20" s="3">
         <v>2017</v>
       </c>
-      <c r="C20" s="60">
+      <c r="C20" s="59">
         <v>333846562289.74597</v>
       </c>
       <c r="D20">
         <v>4.4768991584587638</v>
       </c>
-      <c r="E20" s="60">
+      <c r="E20" s="59">
         <v>88598330696.634109</v>
       </c>
       <c r="F20">
@@ -11175,7 +19690,7 @@
         <f t="shared" si="4"/>
         <v>-3.6148977192293381E-3</v>
       </c>
-      <c r="L20" s="61">
+      <c r="L20" s="60">
         <f t="shared" si="2"/>
         <v>102842.59163064021</v>
       </c>
@@ -11183,7 +19698,7 @@
         <f t="shared" si="5"/>
         <v>4.8559426664513565E-2</v>
       </c>
-      <c r="N20" s="61">
+      <c r="N20" s="60">
         <f t="shared" si="3"/>
         <v>27293.023119651934</v>
       </c>
@@ -11250,13 +19765,13 @@
       <c r="B21" s="3">
         <v>2018</v>
       </c>
-      <c r="C21" s="60">
+      <c r="C21" s="59">
         <v>345370865382.86688</v>
       </c>
       <c r="D21">
         <v>3.4519759658686979</v>
       </c>
-      <c r="E21" s="60">
+      <c r="E21" s="59">
         <v>84207444583.856125</v>
       </c>
       <c r="F21">
@@ -11280,7 +19795,7 @@
         <f t="shared" si="4"/>
         <v>6.652606309509511E-3</v>
       </c>
-      <c r="L21" s="61">
+      <c r="L21" s="60">
         <f t="shared" si="2"/>
         <v>105689.58199636794</v>
       </c>
@@ -11288,7 +19803,7 @@
         <f t="shared" si="5"/>
         <v>2.7682989319762721E-2</v>
       </c>
-      <c r="N21" s="61">
+      <c r="N21" s="60">
         <f t="shared" si="3"/>
         <v>25768.964643801057</v>
       </c>
@@ -11355,13 +19870,13 @@
       <c r="B22" s="3">
         <v>2019</v>
       </c>
-      <c r="C22" s="60">
+      <c r="C22" s="59">
         <v>349888458531.08569</v>
       </c>
       <c r="D22">
         <v>1.3080411815312658</v>
       </c>
-      <c r="E22" s="60">
+      <c r="E22" s="59">
         <v>86300365501.063766</v>
       </c>
       <c r="F22">
@@ -11385,7 +19900,7 @@
         <f t="shared" si="4"/>
         <v>2.4254323011358346E-2</v>
       </c>
-      <c r="L22" s="61">
+      <c r="L22" s="60">
         <f t="shared" si="2"/>
         <v>104536.58124543872</v>
       </c>
@@ -11393,7 +19908,7 @@
         <f t="shared" si="5"/>
         <v>-1.0909313190100821E-2</v>
       </c>
-      <c r="N22" s="61">
+      <c r="N22" s="60">
         <f t="shared" si="3"/>
         <v>25784.060461975751</v>
       </c>
@@ -11460,13 +19975,13 @@
       <c r="B23" s="3">
         <v>2020</v>
       </c>
-      <c r="C23" s="60">
+      <c r="C23" s="59">
         <v>336541232520.5025</v>
       </c>
       <c r="D23">
         <v>-3.8147088551071278</v>
       </c>
-      <c r="E23" s="60">
+      <c r="E23" s="59">
         <v>74186532831.451279</v>
       </c>
       <c r="F23">
@@ -11490,7 +20005,7 @@
         <f t="shared" si="4"/>
         <v>-1.6889283404655522E-2</v>
       </c>
-      <c r="L23" s="61">
+      <c r="L23" s="60">
         <f t="shared" si="2"/>
         <v>102276.18652358696</v>
       </c>
@@ -11498,7 +20013,7 @@
         <f t="shared" si="5"/>
         <v>-2.1623002157920537E-2</v>
       </c>
-      <c r="N23" s="61">
+      <c r="N23" s="60">
         <f t="shared" si="3"/>
         <v>22545.575211041869</v>
       </c>
@@ -11565,13 +20080,13 @@
       <c r="B24" s="3">
         <v>2021</v>
       </c>
-      <c r="C24" s="60">
+      <c r="C24" s="59">
         <v>369376902514.86536</v>
       </c>
       <c r="D24">
         <v>9.7568044629903028</v>
       </c>
-      <c r="E24" s="60">
+      <c r="E24" s="59">
         <v>91394322913.825394</v>
       </c>
       <c r="F24">
@@ -11595,7 +20110,7 @@
         <f t="shared" si="4"/>
         <v>-1.878298325607505E-2</v>
       </c>
-      <c r="L24" s="61">
+      <c r="L24" s="60">
         <f t="shared" si="2"/>
         <v>114403.92098722901</v>
       </c>
@@ -11603,7 +20118,7 @@
         <f t="shared" si="5"/>
         <v>0.11857828176694038</v>
       </c>
-      <c r="N24" s="61">
+      <c r="N24" s="60">
         <f t="shared" si="3"/>
         <v>28306.775074799876</v>
       </c>
@@ -11670,13 +20185,13 @@
       <c r="B25" s="3">
         <v>2022</v>
       </c>
-      <c r="C25" s="60">
+      <c r="C25" s="59">
         <v>384550906479.00623</v>
       </c>
       <c r="D25">
         <v>4.1080002189715117</v>
       </c>
-      <c r="E25" s="60">
+      <c r="E25" s="59">
         <v>95674867710.435883</v>
       </c>
       <c r="F25">
@@ -11700,7 +20215,7 @@
         <f t="shared" si="4"/>
         <v>3.285579637489322E-2</v>
       </c>
-      <c r="L25" s="61">
+      <c r="L25" s="60">
         <f t="shared" si="2"/>
         <v>115314.87234706442</v>
       </c>
@@ -11708,7 +20223,7 @@
         <f t="shared" si="5"/>
         <v>7.9625886243627955E-3</v>
       </c>
-      <c r="N25" s="61">
+      <c r="N25" s="60">
         <f t="shared" si="3"/>
         <v>28689.921076687151</v>
       </c>
@@ -11775,13 +20290,13 @@
       <c r="B26" s="3">
         <v>2023</v>
       </c>
-      <c r="C26" s="60">
+      <c r="C26" s="59">
         <v>391555143381.88489</v>
       </c>
       <c r="D26">
         <v>1.8214069411538532</v>
       </c>
-      <c r="E26" s="60">
+      <c r="E26" s="59">
         <v>94809012056.079865</v>
       </c>
       <c r="F26">
@@ -11805,7 +20320,7 @@
         <f t="shared" si="4"/>
         <v>4.8846829878268612E-2</v>
       </c>
-      <c r="L26" s="61">
+      <c r="L26" s="60">
         <f t="shared" si="2"/>
         <v>111946.97079820893</v>
       </c>
@@ -11813,7 +20328,7 @@
         <f t="shared" si="5"/>
         <v>-2.9206133435408722E-2</v>
       </c>
-      <c r="N26" s="61">
+      <c r="N26" s="60">
         <f t="shared" si="3"/>
         <v>27106.224713022231</v>
       </c>
@@ -11877,13 +20392,13 @@
       <c r="B27" s="3">
         <v>2024</v>
       </c>
-      <c r="C27" s="60">
+      <c r="C27" s="59">
         <v>408736675576.89142</v>
       </c>
       <c r="D27">
         <v>4.3880236246186541</v>
       </c>
-      <c r="E27" s="60">
+      <c r="E27" s="59">
         <v>97592930009.273911</v>
       </c>
       <c r="F27">
@@ -11907,7 +20422,7 @@
         <f t="shared" si="4"/>
         <v>2.5948693402780471E-2</v>
       </c>
-      <c r="L27" s="61">
+      <c r="L27" s="60">
         <f t="shared" si="2"/>
         <v>113903.58121739051</v>
       </c>
@@ -11915,7 +20430,7 @@
         <f t="shared" si="5"/>
         <v>1.7478011287223569E-2</v>
       </c>
-      <c r="N27" s="61">
+      <c r="N27" s="60">
         <f t="shared" si="3"/>
         <v>27196.444297211754</v>
       </c>
@@ -11981,10 +20496,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3B1ED4-C269-4E0D-AF4B-C5E47C42B242}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0722AECA-F9D8-4E94-9029-29AE891E1F4A}">
   <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12492,7 +21018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E65112-9F7A-4E65-AF87-66BF12EAFA09}">
   <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13418,7 +21944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F09706D3-3ACC-423F-8903-C5F506436891}">
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13922,7 +22448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{889850B5-D3B7-45EF-87FA-2DEE08221817}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13933,7 +22459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
